--- a/20260619_SQLSERVER_RechteAudit_V6.xlsx
+++ b/20260619_SQLSERVER_RechteAudit_V6.xlsx
@@ -12,9 +12,9 @@
     <sheet name="Table3" sheetId="3" r:id="rId17"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Table1'!$1:$17</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Table2'!$1:$17</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Table3'!$1:$17</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Table1'!$1:$16</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Table2'!$1:$16</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Table3'!$1:$16</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -1018,10 +1018,9 @@
       <c s="9" t="str" r="U16"/>
       <c s="9" t="str" r="V16"/>
     </row>
-    <row r="17" ht="7" customHeight="1"/>
-    <row r="18" ht="5.65" customHeight="1"/>
-    <row r="19" ht="17" customHeight="1">
-      <c s="10" t="inlineStr" r="B19">
+    <row r="17" ht="5.65" customHeight="1"/>
+    <row r="18" ht="17" customHeight="1">
+      <c s="10" t="inlineStr" r="B18">
         <is>
           <t xml:space="preserve">Globale Berechtigungen.
 Die nachfolgende Tabelle enthält eine Auflistung der User / Gruppen, die grundsätzlichen Zugang auf die betreffenden Datenbanken haben, unabhänging von den tatsächlichen, individuellen Zugriffsrechten.
@@ -1029,67 +1028,67 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="5.65" customHeight="1"/>
+    <row r="19" ht="5.65" customHeight="1"/>
+    <row r="20" ht="17" customHeight="0">
+      <c s="11" t="inlineStr" r="B20">
+        <is>
+          <t xml:space="preserve">AD-Gruppe / AD-User / DB-User</t>
+        </is>
+      </c>
+      <c s="12" t="str" r="C20"/>
+      <c s="13" t="str" r="D20"/>
+      <c s="14" t="inlineStr" r="E20">
+        <is>
+          <t xml:space="preserve">DB-Rolle</t>
+        </is>
+      </c>
+      <c s="14" t="inlineStr" r="F20">
+        <is>
+          <t xml:space="preserve">Recht vergeben an</t>
+        </is>
+      </c>
+      <c s="15" t="str" r="G20"/>
+      <c s="15" t="str" r="H20"/>
+      <c s="16" t="str" r="I20"/>
+      <c s="14" t="inlineStr" r="J20">
+        <is>
+          <t xml:space="preserve">Zugriff</t>
+        </is>
+      </c>
+      <c s="14" t="inlineStr" r="K20">
+        <is>
+          <t xml:space="preserve">Berechtigung</t>
+        </is>
+      </c>
+      <c s="14" t="inlineStr" r="L20">
+        <is>
+          <t xml:space="preserve">Objekttyp</t>
+        </is>
+      </c>
+      <c s="15" t="str" r="M20"/>
+      <c s="16" t="str" r="N20"/>
+      <c s="14" t="inlineStr" r="O20">
+        <is>
+          <t xml:space="preserve">Schema</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P20"/>
+      <c s="14" t="inlineStr" r="Q20">
+        <is>
+          <t xml:space="preserve">Objektname</t>
+        </is>
+      </c>
+      <c s="14" t="inlineStr" r="R20">
+        <is>
+          <t xml:space="preserve">Spalte</t>
+        </is>
+      </c>
+      <c s="15" t="str" r="S20"/>
+      <c s="15" t="str" r="T20"/>
+      <c s="16" t="str" r="U20"/>
+    </row>
     <row r="21" ht="17" customHeight="0">
-      <c s="11" t="inlineStr" r="B21">
-        <is>
-          <t xml:space="preserve">AD-Gruppe / AD-User / DB-User</t>
-        </is>
-      </c>
-      <c s="12" t="str" r="C21"/>
-      <c s="13" t="str" r="D21"/>
-      <c s="14" t="inlineStr" r="E21">
-        <is>
-          <t xml:space="preserve">DB-Rolle</t>
-        </is>
-      </c>
-      <c s="14" t="inlineStr" r="F21">
-        <is>
-          <t xml:space="preserve">Recht vergeben an</t>
-        </is>
-      </c>
-      <c s="15" t="str" r="G21"/>
-      <c s="15" t="str" r="H21"/>
-      <c s="16" t="str" r="I21"/>
-      <c s="14" t="inlineStr" r="J21">
-        <is>
-          <t xml:space="preserve">Zugriff</t>
-        </is>
-      </c>
-      <c s="14" t="inlineStr" r="K21">
-        <is>
-          <t xml:space="preserve">Berechtigung</t>
-        </is>
-      </c>
-      <c s="14" t="inlineStr" r="L21">
-        <is>
-          <t xml:space="preserve">Objekttyp</t>
-        </is>
-      </c>
-      <c s="15" t="str" r="M21"/>
-      <c s="16" t="str" r="N21"/>
-      <c s="14" t="inlineStr" r="O21">
-        <is>
-          <t xml:space="preserve">Schema</t>
-        </is>
-      </c>
-      <c s="16" t="str" r="P21"/>
-      <c s="14" t="inlineStr" r="Q21">
-        <is>
-          <t xml:space="preserve">Objektname</t>
-        </is>
-      </c>
-      <c s="14" t="inlineStr" r="R21">
-        <is>
-          <t xml:space="preserve">Spalte</t>
-        </is>
-      </c>
-      <c s="15" t="str" r="S21"/>
-      <c s="15" t="str" r="T21"/>
-      <c s="16" t="str" r="U21"/>
-    </row>
-    <row r="22" ht="17" customHeight="0">
-      <c s="17" t="inlineStr" r="B22">
+      <c s="17" t="inlineStr" r="B21">
         <is>
           <r>
             <rPr>
@@ -1105,60 +1104,60 @@
           </r>
         </is>
       </c>
-      <c s="12" t="str" r="C22"/>
-      <c s="13" t="str" r="D22"/>
-      <c s="17" t="inlineStr" r="E22">
+      <c s="12" t="str" r="C21"/>
+      <c s="13" t="str" r="D21"/>
+      <c s="17" t="inlineStr" r="E21">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="17" t="inlineStr" r="F22">
+      <c s="17" t="inlineStr" r="F21">
         <is>
           <t xml:space="preserve">SQL_USER</t>
         </is>
       </c>
-      <c s="12" t="str" r="G22"/>
-      <c s="12" t="str" r="H22"/>
-      <c s="13" t="str" r="I22"/>
-      <c s="17" t="inlineStr" r="J22">
-        <is>
-          <t xml:space="preserve">GRANT</t>
-        </is>
-      </c>
-      <c s="17" t="inlineStr" r="K22">
+      <c s="12" t="str" r="G21"/>
+      <c s="12" t="str" r="H21"/>
+      <c s="13" t="str" r="I21"/>
+      <c s="17" t="inlineStr" r="J21">
+        <is>
+          <t xml:space="preserve">GRANT</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="K21">
         <is>
           <t xml:space="preserve">CONNECT</t>
         </is>
       </c>
-      <c s="17" t="inlineStr" r="L22">
+      <c s="17" t="inlineStr" r="L21">
         <is>
           <t xml:space="preserve">DATABASE</t>
         </is>
       </c>
-      <c s="12" t="str" r="M22"/>
-      <c s="13" t="str" r="N22"/>
-      <c s="18" t="inlineStr" r="O22">
-        <is>
-          <t xml:space="preserve">*</t>
-        </is>
-      </c>
-      <c s="13" t="str" r="P22"/>
-      <c s="18" t="inlineStr" r="Q22">
-        <is>
-          <t xml:space="preserve">*</t>
-        </is>
-      </c>
-      <c s="18" t="inlineStr" r="R22">
-        <is>
-          <t xml:space="preserve">*</t>
-        </is>
-      </c>
-      <c s="12" t="str" r="S22"/>
-      <c s="12" t="str" r="T22"/>
-      <c s="13" t="str" r="U22"/>
-    </row>
-    <row r="23" ht="17" customHeight="0">
-      <c s="19" t="inlineStr" r="B23">
+      <c s="12" t="str" r="M21"/>
+      <c s="13" t="str" r="N21"/>
+      <c s="18" t="inlineStr" r="O21">
+        <is>
+          <t xml:space="preserve">*</t>
+        </is>
+      </c>
+      <c s="13" t="str" r="P21"/>
+      <c s="18" t="inlineStr" r="Q21">
+        <is>
+          <t xml:space="preserve">*</t>
+        </is>
+      </c>
+      <c s="18" t="inlineStr" r="R21">
+        <is>
+          <t xml:space="preserve">*</t>
+        </is>
+      </c>
+      <c s="12" t="str" r="S21"/>
+      <c s="12" t="str" r="T21"/>
+      <c s="13" t="str" r="U21"/>
+    </row>
+    <row r="22" ht="17" customHeight="0">
+      <c s="19" t="inlineStr" r="B22">
         <is>
           <r>
             <rPr>
@@ -1174,60 +1173,60 @@
           </r>
         </is>
       </c>
-      <c s="12" t="str" r="C23"/>
-      <c s="13" t="str" r="D23"/>
-      <c s="19" t="inlineStr" r="E23">
+      <c s="12" t="str" r="C22"/>
+      <c s="13" t="str" r="D22"/>
+      <c s="19" t="inlineStr" r="E22">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="19" t="inlineStr" r="F23">
+      <c s="19" t="inlineStr" r="F22">
         <is>
           <t xml:space="preserve">WINDOWS_USER</t>
         </is>
       </c>
-      <c s="12" t="str" r="G23"/>
-      <c s="12" t="str" r="H23"/>
-      <c s="13" t="str" r="I23"/>
-      <c s="19" t="inlineStr" r="J23">
-        <is>
-          <t xml:space="preserve">GRANT</t>
-        </is>
-      </c>
-      <c s="19" t="inlineStr" r="K23">
+      <c s="12" t="str" r="G22"/>
+      <c s="12" t="str" r="H22"/>
+      <c s="13" t="str" r="I22"/>
+      <c s="19" t="inlineStr" r="J22">
+        <is>
+          <t xml:space="preserve">GRANT</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K22">
         <is>
           <t xml:space="preserve">CONNECT</t>
         </is>
       </c>
-      <c s="19" t="inlineStr" r="L23">
+      <c s="19" t="inlineStr" r="L22">
         <is>
           <t xml:space="preserve">DATABASE</t>
         </is>
       </c>
-      <c s="12" t="str" r="M23"/>
-      <c s="13" t="str" r="N23"/>
-      <c s="20" t="inlineStr" r="O23">
-        <is>
-          <t xml:space="preserve">*</t>
-        </is>
-      </c>
-      <c s="13" t="str" r="P23"/>
-      <c s="20" t="inlineStr" r="Q23">
-        <is>
-          <t xml:space="preserve">*</t>
-        </is>
-      </c>
-      <c s="20" t="inlineStr" r="R23">
-        <is>
-          <t xml:space="preserve">*</t>
-        </is>
-      </c>
-      <c s="12" t="str" r="S23"/>
-      <c s="12" t="str" r="T23"/>
-      <c s="13" t="str" r="U23"/>
-    </row>
-    <row r="24" ht="17" customHeight="0">
-      <c s="19" t="inlineStr" r="B24">
+      <c s="12" t="str" r="M22"/>
+      <c s="13" t="str" r="N22"/>
+      <c s="20" t="inlineStr" r="O22">
+        <is>
+          <t xml:space="preserve">*</t>
+        </is>
+      </c>
+      <c s="13" t="str" r="P22"/>
+      <c s="20" t="inlineStr" r="Q22">
+        <is>
+          <t xml:space="preserve">*</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="R22">
+        <is>
+          <t xml:space="preserve">*</t>
+        </is>
+      </c>
+      <c s="12" t="str" r="S22"/>
+      <c s="12" t="str" r="T22"/>
+      <c s="13" t="str" r="U22"/>
+    </row>
+    <row r="23" ht="17" customHeight="0">
+      <c s="19" t="inlineStr" r="B23">
         <is>
           <r>
             <rPr>
@@ -1243,59 +1242,59 @@
           </r>
         </is>
       </c>
-      <c s="12" t="str" r="C24"/>
-      <c s="13" t="str" r="D24"/>
-      <c s="19" t="inlineStr" r="E24">
+      <c s="12" t="str" r="C23"/>
+      <c s="13" t="str" r="D23"/>
+      <c s="19" t="inlineStr" r="E23">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="19" t="inlineStr" r="F24">
+      <c s="19" t="inlineStr" r="F23">
         <is>
           <t xml:space="preserve">WINDOWS_USER</t>
         </is>
       </c>
-      <c s="12" t="str" r="G24"/>
-      <c s="12" t="str" r="H24"/>
-      <c s="13" t="str" r="I24"/>
-      <c s="19" t="inlineStr" r="J24">
-        <is>
-          <t xml:space="preserve">GRANT</t>
-        </is>
-      </c>
-      <c s="19" t="inlineStr" r="K24">
+      <c s="12" t="str" r="G23"/>
+      <c s="12" t="str" r="H23"/>
+      <c s="13" t="str" r="I23"/>
+      <c s="19" t="inlineStr" r="J23">
+        <is>
+          <t xml:space="preserve">GRANT</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K23">
         <is>
           <t xml:space="preserve">CONNECT</t>
         </is>
       </c>
-      <c s="19" t="inlineStr" r="L24">
+      <c s="19" t="inlineStr" r="L23">
         <is>
           <t xml:space="preserve">DATABASE</t>
         </is>
       </c>
-      <c s="12" t="str" r="M24"/>
-      <c s="13" t="str" r="N24"/>
-      <c s="20" t="inlineStr" r="O24">
-        <is>
-          <t xml:space="preserve">*</t>
-        </is>
-      </c>
-      <c s="13" t="str" r="P24"/>
-      <c s="20" t="inlineStr" r="Q24">
-        <is>
-          <t xml:space="preserve">*</t>
-        </is>
-      </c>
-      <c s="20" t="inlineStr" r="R24">
-        <is>
-          <t xml:space="preserve">*</t>
-        </is>
-      </c>
-      <c s="12" t="str" r="S24"/>
-      <c s="12" t="str" r="T24"/>
-      <c s="13" t="str" r="U24"/>
-    </row>
-    <row r="25" ht="0.05" customHeight="1"/>
+      <c s="12" t="str" r="M23"/>
+      <c s="13" t="str" r="N23"/>
+      <c s="20" t="inlineStr" r="O23">
+        <is>
+          <t xml:space="preserve">*</t>
+        </is>
+      </c>
+      <c s="13" t="str" r="P23"/>
+      <c s="20" t="inlineStr" r="Q23">
+        <is>
+          <t xml:space="preserve">*</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="R23">
+        <is>
+          <t xml:space="preserve">*</t>
+        </is>
+      </c>
+      <c s="12" t="str" r="S23"/>
+      <c s="12" t="str" r="T23"/>
+      <c s="13" t="str" r="U23"/>
+    </row>
+    <row r="24" ht="0.05" customHeight="1"/>
   </sheetData>
   <mergeCells>
     <mergeCell ref="T1:T6"/>
@@ -1318,7 +1317,12 @@
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="H14:L14"/>
     <mergeCell ref="C16:V16"/>
-    <mergeCell ref="B19:U19"/>
+    <mergeCell ref="B18:U18"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="F20:I20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:P20"/>
+    <mergeCell ref="R20:U20"/>
     <mergeCell ref="B21:D21"/>
     <mergeCell ref="F21:I21"/>
     <mergeCell ref="L21:N21"/>
@@ -1334,23 +1338,18 @@
     <mergeCell ref="L23:N23"/>
     <mergeCell ref="O23:P23"/>
     <mergeCell ref="R23:U23"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="F24:I24"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="O24:P24"/>
-    <mergeCell ref="R24:U24"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="B22" r:id="rId10"/>
-    <hyperlink ref="B23" r:id="rId11"/>
-    <hyperlink ref="B24" r:id="rId12"/>
+    <hyperlink ref="B21" r:id="rId10"/>
+    <hyperlink ref="B22" r:id="rId11"/>
+    <hyperlink ref="B23" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0" right="0" top="0" bottom="0.766566929133858" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
     <oddFooter>&amp;L&amp;"Arial,Regular"&amp;7 Bericht '/SQLSERVER_RechteAudit_V6' 
 &amp;"-,Regular"Berichtsverantwortlicher: Markus Hofmann (IB15MH) &amp;C&amp;"Arial,Regular"&amp;10  &amp;R&amp;"Arial,Regular"&amp;7 Generiert von LAN\\ps733 
-&amp;"-,Regular"19.06.2026 10:59:29 Uhr 
+&amp;"-,Regular"19.06.2026 11:01:25 Uhr 
 &amp;"-,Regular"Seite &amp;P von &amp;N </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
@@ -1613,10 +1612,9 @@
       <c s="9" t="str" r="U16"/>
       <c s="9" t="str" r="V16"/>
     </row>
-    <row r="17" ht="7" customHeight="1"/>
-    <row r="18" ht="5.65" customHeight="1"/>
-    <row r="19" ht="17" customHeight="1">
-      <c s="10" t="inlineStr" r="B19">
+    <row r="17" ht="5.65" customHeight="1"/>
+    <row r="18" ht="17" customHeight="1">
+      <c s="10" t="inlineStr" r="B18">
         <is>
           <t xml:space="preserve">Objektberechtigungen.
 Im Folgenden sind die individuellen Rechte aufgefuhrt, die an die User / Gruppen entweder direkt order indirekt über Datenbankrollen vergeben sind.
@@ -1624,67 +1622,67 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="5.65" customHeight="1"/>
+    <row r="19" ht="5.65" customHeight="1"/>
+    <row r="20" ht="17" customHeight="0">
+      <c s="14" t="inlineStr" r="B20">
+        <is>
+          <t xml:space="preserve">AD-Gruppe / AD-User / DB-User</t>
+        </is>
+      </c>
+      <c s="15" t="str" r="C20"/>
+      <c s="16" t="str" r="D20"/>
+      <c s="14" t="inlineStr" r="E20">
+        <is>
+          <t xml:space="preserve">DB-Rolle</t>
+        </is>
+      </c>
+      <c s="14" t="inlineStr" r="F20">
+        <is>
+          <t xml:space="preserve">Recht vergeben an</t>
+        </is>
+      </c>
+      <c s="15" t="str" r="G20"/>
+      <c s="15" t="str" r="H20"/>
+      <c s="16" t="str" r="I20"/>
+      <c s="14" t="inlineStr" r="J20">
+        <is>
+          <t xml:space="preserve">Zugriff</t>
+        </is>
+      </c>
+      <c s="14" t="inlineStr" r="K20">
+        <is>
+          <t xml:space="preserve">Berechtigung</t>
+        </is>
+      </c>
+      <c s="14" t="inlineStr" r="L20">
+        <is>
+          <t xml:space="preserve">Objekttyp</t>
+        </is>
+      </c>
+      <c s="15" t="str" r="M20"/>
+      <c s="16" t="str" r="N20"/>
+      <c s="14" t="inlineStr" r="O20">
+        <is>
+          <t xml:space="preserve">Schema</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P20"/>
+      <c s="14" t="inlineStr" r="Q20">
+        <is>
+          <t xml:space="preserve">Objektname</t>
+        </is>
+      </c>
+      <c s="14" t="inlineStr" r="R20">
+        <is>
+          <t xml:space="preserve">Spalte</t>
+        </is>
+      </c>
+      <c s="15" t="str" r="S20"/>
+      <c s="15" t="str" r="T20"/>
+      <c s="16" t="str" r="U20"/>
+    </row>
     <row r="21" ht="17" customHeight="0">
-      <c s="14" t="inlineStr" r="B21">
-        <is>
-          <t xml:space="preserve">AD-Gruppe / AD-User / DB-User</t>
-        </is>
-      </c>
-      <c s="15" t="str" r="C21"/>
-      <c s="16" t="str" r="D21"/>
-      <c s="14" t="inlineStr" r="E21">
-        <is>
-          <t xml:space="preserve">DB-Rolle</t>
-        </is>
-      </c>
-      <c s="14" t="inlineStr" r="F21">
-        <is>
-          <t xml:space="preserve">Recht vergeben an</t>
-        </is>
-      </c>
-      <c s="15" t="str" r="G21"/>
-      <c s="15" t="str" r="H21"/>
-      <c s="16" t="str" r="I21"/>
-      <c s="14" t="inlineStr" r="J21">
-        <is>
-          <t xml:space="preserve">Zugriff</t>
-        </is>
-      </c>
-      <c s="14" t="inlineStr" r="K21">
-        <is>
-          <t xml:space="preserve">Berechtigung</t>
-        </is>
-      </c>
-      <c s="14" t="inlineStr" r="L21">
-        <is>
-          <t xml:space="preserve">Objekttyp</t>
-        </is>
-      </c>
-      <c s="15" t="str" r="M21"/>
-      <c s="16" t="str" r="N21"/>
-      <c s="14" t="inlineStr" r="O21">
-        <is>
-          <t xml:space="preserve">Schema</t>
-        </is>
-      </c>
-      <c s="16" t="str" r="P21"/>
-      <c s="14" t="inlineStr" r="Q21">
-        <is>
-          <t xml:space="preserve">Objektname</t>
-        </is>
-      </c>
-      <c s="14" t="inlineStr" r="R21">
-        <is>
-          <t xml:space="preserve">Spalte</t>
-        </is>
-      </c>
-      <c s="15" t="str" r="S21"/>
-      <c s="15" t="str" r="T21"/>
-      <c s="16" t="str" r="U21"/>
-    </row>
-    <row r="22" ht="17" customHeight="0">
-      <c s="17" t="inlineStr" r="B22">
+      <c s="17" t="inlineStr" r="B21">
         <is>
           <r>
             <rPr>
@@ -1700,60 +1698,60 @@
           </r>
         </is>
       </c>
-      <c s="12" t="str" r="C22"/>
-      <c s="13" t="str" r="D22"/>
-      <c s="17" t="inlineStr" r="E22">
+      <c s="12" t="str" r="C21"/>
+      <c s="13" t="str" r="D21"/>
+      <c s="17" t="inlineStr" r="E21">
         <is>
           <t xml:space="preserve">ro_Columns</t>
         </is>
       </c>
-      <c s="17" t="inlineStr" r="F22">
+      <c s="17" t="inlineStr" r="F21">
         <is>
           <t xml:space="preserve">SQL_USER</t>
         </is>
       </c>
-      <c s="12" t="str" r="G22"/>
-      <c s="12" t="str" r="H22"/>
-      <c s="13" t="str" r="I22"/>
-      <c s="17" t="inlineStr" r="J22">
-        <is>
-          <t xml:space="preserve">GRANT</t>
-        </is>
-      </c>
-      <c s="17" t="inlineStr" r="K22">
-        <is>
-          <t xml:space="preserve">SELECT</t>
-        </is>
-      </c>
-      <c s="17" t="inlineStr" r="L22">
+      <c s="12" t="str" r="G21"/>
+      <c s="12" t="str" r="H21"/>
+      <c s="13" t="str" r="I21"/>
+      <c s="17" t="inlineStr" r="J21">
+        <is>
+          <t xml:space="preserve">GRANT</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="K21">
+        <is>
+          <t xml:space="preserve">SELECT</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="L21">
         <is>
           <t xml:space="preserve">USER_TABLE</t>
         </is>
       </c>
-      <c s="12" t="str" r="M22"/>
-      <c s="13" t="str" r="N22"/>
-      <c s="17" t="inlineStr" r="O22">
+      <c s="12" t="str" r="M21"/>
+      <c s="13" t="str" r="N21"/>
+      <c s="17" t="inlineStr" r="O21">
         <is>
           <t xml:space="preserve">TestSchema</t>
         </is>
       </c>
-      <c s="13" t="str" r="P22"/>
-      <c s="17" t="inlineStr" r="Q22">
+      <c s="13" t="str" r="P21"/>
+      <c s="17" t="inlineStr" r="Q21">
         <is>
           <t xml:space="preserve">t1</t>
         </is>
       </c>
-      <c s="17" t="inlineStr" r="R22">
+      <c s="17" t="inlineStr" r="R21">
         <is>
           <t xml:space="preserve">s1</t>
         </is>
       </c>
-      <c s="12" t="str" r="S22"/>
-      <c s="12" t="str" r="T22"/>
-      <c s="13" t="str" r="U22"/>
-    </row>
-    <row r="23" ht="17" customHeight="0">
-      <c s="19" t="inlineStr" r="B23">
+      <c s="12" t="str" r="S21"/>
+      <c s="12" t="str" r="T21"/>
+      <c s="13" t="str" r="U21"/>
+    </row>
+    <row r="22" ht="17" customHeight="0">
+      <c s="19" t="inlineStr" r="B22">
         <is>
           <r>
             <rPr>
@@ -1769,17 +1767,63 @@
           </r>
         </is>
       </c>
-      <c s="21" t="str" r="C23"/>
-      <c s="22" t="str" r="D23"/>
-      <c s="19" t="str" r="E23"/>
-      <c s="19" t="inlineStr" r="F23">
+      <c s="21" t="str" r="C22"/>
+      <c s="22" t="str" r="D22"/>
+      <c s="19" t="str" r="E22"/>
+      <c s="19" t="inlineStr" r="F22">
         <is>
           <t xml:space="preserve">DATABASE_ROLE</t>
         </is>
       </c>
-      <c s="21" t="str" r="G23"/>
-      <c s="21" t="str" r="H23"/>
-      <c s="22" t="str" r="I23"/>
+      <c s="21" t="str" r="G22"/>
+      <c s="21" t="str" r="H22"/>
+      <c s="22" t="str" r="I22"/>
+      <c s="19" t="inlineStr" r="J22">
+        <is>
+          <t xml:space="preserve">GRANT</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K22">
+        <is>
+          <t xml:space="preserve">SHOWPLAN</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="L22">
+        <is>
+          <t xml:space="preserve">DATABASE</t>
+        </is>
+      </c>
+      <c s="12" t="str" r="M22"/>
+      <c s="13" t="str" r="N22"/>
+      <c s="20" t="inlineStr" r="O22">
+        <is>
+          <t xml:space="preserve">*</t>
+        </is>
+      </c>
+      <c s="13" t="str" r="P22"/>
+      <c s="20" t="inlineStr" r="Q22">
+        <is>
+          <t xml:space="preserve">*</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="R22">
+        <is>
+          <t xml:space="preserve">*</t>
+        </is>
+      </c>
+      <c s="12" t="str" r="S22"/>
+      <c s="12" t="str" r="T22"/>
+      <c s="13" t="str" r="U22"/>
+    </row>
+    <row r="23" ht="17.05" customHeight="0">
+      <c s="23" t="str" r="B23"/>
+      <c s="24" t="str" r="C23"/>
+      <c s="25" t="str" r="D23"/>
+      <c s="26" t="str" r="E23"/>
+      <c s="23" t="str" r="F23"/>
+      <c s="24" t="str" r="G23"/>
+      <c s="24" t="str" r="H23"/>
+      <c s="25" t="str" r="I23"/>
       <c s="19" t="inlineStr" r="J23">
         <is>
           <t xml:space="preserve">GRANT</t>
@@ -1787,7 +1831,7 @@
       </c>
       <c s="19" t="inlineStr" r="K23">
         <is>
-          <t xml:space="preserve">SHOWPLAN</t>
+          <t xml:space="preserve">VIEW DATABASE STATE</t>
         </is>
       </c>
       <c s="19" t="inlineStr" r="L23">
@@ -1817,54 +1861,8 @@
       <c s="12" t="str" r="T23"/>
       <c s="13" t="str" r="U23"/>
     </row>
-    <row r="24" ht="17.05" customHeight="0">
-      <c s="23" t="str" r="B24"/>
-      <c s="24" t="str" r="C24"/>
-      <c s="25" t="str" r="D24"/>
-      <c s="26" t="str" r="E24"/>
-      <c s="23" t="str" r="F24"/>
-      <c s="24" t="str" r="G24"/>
-      <c s="24" t="str" r="H24"/>
-      <c s="25" t="str" r="I24"/>
-      <c s="19" t="inlineStr" r="J24">
-        <is>
-          <t xml:space="preserve">GRANT</t>
-        </is>
-      </c>
-      <c s="19" t="inlineStr" r="K24">
-        <is>
-          <t xml:space="preserve">VIEW DATABASE STATE</t>
-        </is>
-      </c>
-      <c s="19" t="inlineStr" r="L24">
-        <is>
-          <t xml:space="preserve">DATABASE</t>
-        </is>
-      </c>
-      <c s="12" t="str" r="M24"/>
-      <c s="13" t="str" r="N24"/>
-      <c s="20" t="inlineStr" r="O24">
-        <is>
-          <t xml:space="preserve">*</t>
-        </is>
-      </c>
-      <c s="13" t="str" r="P24"/>
-      <c s="20" t="inlineStr" r="Q24">
-        <is>
-          <t xml:space="preserve">*</t>
-        </is>
-      </c>
-      <c s="20" t="inlineStr" r="R24">
-        <is>
-          <t xml:space="preserve">*</t>
-        </is>
-      </c>
-      <c s="12" t="str" r="S24"/>
-      <c s="12" t="str" r="T24"/>
-      <c s="13" t="str" r="U24"/>
-    </row>
-    <row r="25" ht="17" customHeight="0">
-      <c s="19" t="inlineStr" r="B25">
+    <row r="24" ht="17" customHeight="0">
+      <c s="19" t="inlineStr" r="B24">
         <is>
           <r>
             <rPr>
@@ -1880,21 +1878,64 @@
           </r>
         </is>
       </c>
-      <c s="21" t="str" r="C25"/>
-      <c s="22" t="str" r="D25"/>
-      <c s="19" t="inlineStr" r="E25">
+      <c s="21" t="str" r="C24"/>
+      <c s="22" t="str" r="D24"/>
+      <c s="19" t="inlineStr" r="E24">
         <is>
           <t xml:space="preserve">ro_Columns</t>
         </is>
       </c>
-      <c s="19" t="inlineStr" r="F25">
+      <c s="19" t="inlineStr" r="F24">
         <is>
           <t xml:space="preserve">SQL_USER</t>
         </is>
       </c>
-      <c s="21" t="str" r="G25"/>
-      <c s="21" t="str" r="H25"/>
-      <c s="22" t="str" r="I25"/>
+      <c s="21" t="str" r="G24"/>
+      <c s="21" t="str" r="H24"/>
+      <c s="22" t="str" r="I24"/>
+      <c s="19" t="inlineStr" r="J24">
+        <is>
+          <t xml:space="preserve">GRANT</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K24">
+        <is>
+          <t xml:space="preserve">SELECT</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="L24">
+        <is>
+          <t xml:space="preserve">USER_TABLE</t>
+        </is>
+      </c>
+      <c s="12" t="str" r="M24"/>
+      <c s="13" t="str" r="N24"/>
+      <c s="19" t="inlineStr" r="O24">
+        <is>
+          <t xml:space="preserve">dbo</t>
+        </is>
+      </c>
+      <c s="13" t="str" r="P24"/>
+      <c s="19" t="inlineStr" r="Q24">
+        <is>
+          <t xml:space="preserve">t1</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="R24">
+        <is>
+          <t xml:space="preserve">s1</t>
+        </is>
+      </c>
+      <c s="12" t="str" r="S24"/>
+      <c s="12" t="str" r="T24"/>
+      <c s="13" t="str" r="U24"/>
+    </row>
+    <row r="25" ht="17" customHeight="0">
+      <c s="27" t="str" r="B25"/>
+      <c s="28" t="str" r="D25"/>
+      <c s="29" t="str" r="E25"/>
+      <c s="27" t="str" r="F25"/>
+      <c s="28" t="str" r="I25"/>
       <c s="19" t="inlineStr" r="J25">
         <is>
           <t xml:space="preserve">GRANT</t>
@@ -1920,12 +1961,12 @@
       <c s="13" t="str" r="P25"/>
       <c s="19" t="inlineStr" r="Q25">
         <is>
-          <t xml:space="preserve">t1</t>
+          <t xml:space="preserve">t2</t>
         </is>
       </c>
       <c s="19" t="inlineStr" r="R25">
         <is>
-          <t xml:space="preserve">s1</t>
+          <t xml:space="preserve">s2</t>
         </is>
       </c>
       <c s="12" t="str" r="S25"/>
@@ -1935,9 +1976,11 @@
     <row r="26" ht="17" customHeight="0">
       <c s="27" t="str" r="B26"/>
       <c s="28" t="str" r="D26"/>
-      <c s="29" t="str" r="E26"/>
-      <c s="27" t="str" r="F26"/>
-      <c s="28" t="str" r="I26"/>
+      <c s="26" t="str" r="E26"/>
+      <c s="23" t="str" r="F26"/>
+      <c s="24" t="str" r="G26"/>
+      <c s="24" t="str" r="H26"/>
+      <c s="25" t="str" r="I26"/>
       <c s="19" t="inlineStr" r="J26">
         <is>
           <t xml:space="preserve">GRANT</t>
@@ -1957,7 +2000,7 @@
       <c s="13" t="str" r="N26"/>
       <c s="19" t="inlineStr" r="O26">
         <is>
-          <t xml:space="preserve">dbo</t>
+          <t xml:space="preserve">TestSchema</t>
         </is>
       </c>
       <c s="13" t="str" r="P26"/>
@@ -1978,11 +2021,19 @@
     <row r="27" ht="17" customHeight="0">
       <c s="27" t="str" r="B27"/>
       <c s="28" t="str" r="D27"/>
-      <c s="26" t="str" r="E27"/>
-      <c s="23" t="str" r="F27"/>
-      <c s="24" t="str" r="G27"/>
-      <c s="24" t="str" r="H27"/>
-      <c s="25" t="str" r="I27"/>
+      <c s="19" t="inlineStr" r="E27">
+        <is>
+          <t xml:space="preserve">ro_Schema</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="F27">
+        <is>
+          <t xml:space="preserve">SQL_USER</t>
+        </is>
+      </c>
+      <c s="12" t="str" r="G27"/>
+      <c s="12" t="str" r="H27"/>
+      <c s="13" t="str" r="I27"/>
       <c s="19" t="inlineStr" r="J27">
         <is>
           <t xml:space="preserve">GRANT</t>
@@ -1995,25 +2046,25 @@
       </c>
       <c s="19" t="inlineStr" r="L27">
         <is>
-          <t xml:space="preserve">USER_TABLE</t>
+          <t xml:space="preserve">SYSTEM_TABLE</t>
         </is>
       </c>
       <c s="12" t="str" r="M27"/>
       <c s="13" t="str" r="N27"/>
       <c s="19" t="inlineStr" r="O27">
         <is>
-          <t xml:space="preserve">TestSchema</t>
+          <t xml:space="preserve">sys</t>
         </is>
       </c>
       <c s="13" t="str" r="P27"/>
       <c s="19" t="inlineStr" r="Q27">
         <is>
-          <t xml:space="preserve">t2</t>
-        </is>
-      </c>
-      <c s="19" t="inlineStr" r="R27">
-        <is>
-          <t xml:space="preserve">s2</t>
+          <t xml:space="preserve">sysrowsets</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="R27">
+        <is>
+          <t xml:space="preserve">*</t>
         </is>
       </c>
       <c s="12" t="str" r="S27"/>
@@ -2025,7 +2076,7 @@
       <c s="28" t="str" r="D28"/>
       <c s="19" t="inlineStr" r="E28">
         <is>
-          <t xml:space="preserve">ro_Schema</t>
+          <t xml:space="preserve">ro_SPs</t>
         </is>
       </c>
       <c s="19" t="inlineStr" r="F28">
@@ -2033,9 +2084,9 @@
           <t xml:space="preserve">SQL_USER</t>
         </is>
       </c>
-      <c s="12" t="str" r="G28"/>
-      <c s="12" t="str" r="H28"/>
-      <c s="13" t="str" r="I28"/>
+      <c s="21" t="str" r="G28"/>
+      <c s="21" t="str" r="H28"/>
+      <c s="22" t="str" r="I28"/>
       <c s="19" t="inlineStr" r="J28">
         <is>
           <t xml:space="preserve">GRANT</t>
@@ -2043,25 +2094,25 @@
       </c>
       <c s="19" t="inlineStr" r="K28">
         <is>
-          <t xml:space="preserve">SELECT</t>
+          <t xml:space="preserve">EXECUTE</t>
         </is>
       </c>
       <c s="19" t="inlineStr" r="L28">
         <is>
-          <t xml:space="preserve">SYSTEM_TABLE</t>
+          <t xml:space="preserve">SQL_STORED_PROCEDURE</t>
         </is>
       </c>
       <c s="12" t="str" r="M28"/>
       <c s="13" t="str" r="N28"/>
       <c s="19" t="inlineStr" r="O28">
         <is>
-          <t xml:space="preserve">sys</t>
+          <t xml:space="preserve">dbo</t>
         </is>
       </c>
       <c s="13" t="str" r="P28"/>
       <c s="19" t="inlineStr" r="Q28">
         <is>
-          <t xml:space="preserve">sysrowsets</t>
+          <t xml:space="preserve">usp1</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R28">
@@ -2073,22 +2124,12 @@
       <c s="12" t="str" r="T28"/>
       <c s="13" t="str" r="U28"/>
     </row>
-    <row r="29" ht="17" customHeight="0">
+    <row r="29" ht="17.05" customHeight="0">
       <c s="27" t="str" r="B29"/>
       <c s="28" t="str" r="D29"/>
-      <c s="19" t="inlineStr" r="E29">
-        <is>
-          <t xml:space="preserve">ro_SPs</t>
-        </is>
-      </c>
-      <c s="19" t="inlineStr" r="F29">
-        <is>
-          <t xml:space="preserve">SQL_USER</t>
-        </is>
-      </c>
-      <c s="21" t="str" r="G29"/>
-      <c s="21" t="str" r="H29"/>
-      <c s="22" t="str" r="I29"/>
+      <c s="29" t="str" r="E29"/>
+      <c s="27" t="str" r="F29"/>
+      <c s="28" t="str" r="I29"/>
       <c s="19" t="inlineStr" r="J29">
         <is>
           <t xml:space="preserve">GRANT</t>
@@ -2114,7 +2155,7 @@
       <c s="13" t="str" r="P29"/>
       <c s="19" t="inlineStr" r="Q29">
         <is>
-          <t xml:space="preserve">usp1</t>
+          <t xml:space="preserve">usp2</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R29">
@@ -2126,7 +2167,7 @@
       <c s="12" t="str" r="T29"/>
       <c s="13" t="str" r="U29"/>
     </row>
-    <row r="30" ht="17.05" customHeight="0">
+    <row r="30" ht="17" customHeight="0">
       <c s="27" t="str" r="B30"/>
       <c s="28" t="str" r="D30"/>
       <c s="29" t="str" r="E30"/>
@@ -2139,7 +2180,7 @@
       </c>
       <c s="19" t="inlineStr" r="K30">
         <is>
-          <t xml:space="preserve">EXECUTE</t>
+          <t xml:space="preserve">ALTER</t>
         </is>
       </c>
       <c s="19" t="inlineStr" r="L30">
@@ -2151,13 +2192,13 @@
       <c s="13" t="str" r="N30"/>
       <c s="19" t="inlineStr" r="O30">
         <is>
-          <t xml:space="preserve">dbo</t>
+          <t xml:space="preserve">TestSchema</t>
         </is>
       </c>
       <c s="13" t="str" r="P30"/>
       <c s="19" t="inlineStr" r="Q30">
         <is>
-          <t xml:space="preserve">usp2</t>
+          <t xml:space="preserve">usp1</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R30">
@@ -2182,7 +2223,7 @@
       </c>
       <c s="19" t="inlineStr" r="K31">
         <is>
-          <t xml:space="preserve">ALTER</t>
+          <t xml:space="preserve">EXECUTE</t>
         </is>
       </c>
       <c s="19" t="inlineStr" r="L31">
@@ -2225,7 +2266,7 @@
       </c>
       <c s="19" t="inlineStr" r="K32">
         <is>
-          <t xml:space="preserve">EXECUTE</t>
+          <t xml:space="preserve">ALTER</t>
         </is>
       </c>
       <c s="19" t="inlineStr" r="L32">
@@ -2243,7 +2284,7 @@
       <c s="13" t="str" r="P32"/>
       <c s="19" t="inlineStr" r="Q32">
         <is>
-          <t xml:space="preserve">usp1</t>
+          <t xml:space="preserve">usp2</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R32">
@@ -2258,9 +2299,11 @@
     <row r="33" ht="17" customHeight="0">
       <c s="27" t="str" r="B33"/>
       <c s="28" t="str" r="D33"/>
-      <c s="29" t="str" r="E33"/>
-      <c s="27" t="str" r="F33"/>
-      <c s="28" t="str" r="I33"/>
+      <c s="26" t="str" r="E33"/>
+      <c s="23" t="str" r="F33"/>
+      <c s="24" t="str" r="G33"/>
+      <c s="24" t="str" r="H33"/>
+      <c s="25" t="str" r="I33"/>
       <c s="19" t="inlineStr" r="J33">
         <is>
           <t xml:space="preserve">GRANT</t>
@@ -2268,7 +2311,7 @@
       </c>
       <c s="19" t="inlineStr" r="K33">
         <is>
-          <t xml:space="preserve">ALTER</t>
+          <t xml:space="preserve">EXECUTE</t>
         </is>
       </c>
       <c s="19" t="inlineStr" r="L33">
@@ -2301,11 +2344,19 @@
     <row r="34" ht="17" customHeight="0">
       <c s="27" t="str" r="B34"/>
       <c s="28" t="str" r="D34"/>
-      <c s="26" t="str" r="E34"/>
-      <c s="23" t="str" r="F34"/>
-      <c s="24" t="str" r="G34"/>
-      <c s="24" t="str" r="H34"/>
-      <c s="25" t="str" r="I34"/>
+      <c s="19" t="inlineStr" r="E34">
+        <is>
+          <t xml:space="preserve">ro_Tables</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="F34">
+        <is>
+          <t xml:space="preserve">SQL_USER</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="G34"/>
+      <c s="21" t="str" r="H34"/>
+      <c s="22" t="str" r="I34"/>
       <c s="19" t="inlineStr" r="J34">
         <is>
           <t xml:space="preserve">GRANT</t>
@@ -2313,25 +2364,25 @@
       </c>
       <c s="19" t="inlineStr" r="K34">
         <is>
-          <t xml:space="preserve">EXECUTE</t>
+          <t xml:space="preserve">DELETE</t>
         </is>
       </c>
       <c s="19" t="inlineStr" r="L34">
         <is>
-          <t xml:space="preserve">SQL_STORED_PROCEDURE</t>
+          <t xml:space="preserve">USER_TABLE</t>
         </is>
       </c>
       <c s="12" t="str" r="M34"/>
       <c s="13" t="str" r="N34"/>
       <c s="19" t="inlineStr" r="O34">
         <is>
-          <t xml:space="preserve">TestSchema</t>
+          <t xml:space="preserve">dbo</t>
         </is>
       </c>
       <c s="13" t="str" r="P34"/>
       <c s="19" t="inlineStr" r="Q34">
         <is>
-          <t xml:space="preserve">usp2</t>
+          <t xml:space="preserve">t1</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R34">
@@ -2343,22 +2394,12 @@
       <c s="12" t="str" r="T34"/>
       <c s="13" t="str" r="U34"/>
     </row>
-    <row r="35" ht="17" customHeight="0">
+    <row r="35" ht="17.05" customHeight="0">
       <c s="27" t="str" r="B35"/>
       <c s="28" t="str" r="D35"/>
-      <c s="19" t="inlineStr" r="E35">
-        <is>
-          <t xml:space="preserve">ro_Tables</t>
-        </is>
-      </c>
-      <c s="19" t="inlineStr" r="F35">
-        <is>
-          <t xml:space="preserve">SQL_USER</t>
-        </is>
-      </c>
-      <c s="21" t="str" r="G35"/>
-      <c s="21" t="str" r="H35"/>
-      <c s="22" t="str" r="I35"/>
+      <c s="29" t="str" r="E35"/>
+      <c s="27" t="str" r="F35"/>
+      <c s="28" t="str" r="I35"/>
       <c s="19" t="inlineStr" r="J35">
         <is>
           <t xml:space="preserve">GRANT</t>
@@ -2366,7 +2407,7 @@
       </c>
       <c s="19" t="inlineStr" r="K35">
         <is>
-          <t xml:space="preserve">DELETE</t>
+          <t xml:space="preserve">INSERT</t>
         </is>
       </c>
       <c s="19" t="inlineStr" r="L35">
@@ -2396,7 +2437,7 @@
       <c s="12" t="str" r="T35"/>
       <c s="13" t="str" r="U35"/>
     </row>
-    <row r="36" ht="17.05" customHeight="0">
+    <row r="36" ht="17" customHeight="0">
       <c s="27" t="str" r="B36"/>
       <c s="28" t="str" r="D36"/>
       <c s="29" t="str" r="E36"/>
@@ -2409,7 +2450,7 @@
       </c>
       <c s="19" t="inlineStr" r="K36">
         <is>
-          <t xml:space="preserve">INSERT</t>
+          <t xml:space="preserve">SELECT</t>
         </is>
       </c>
       <c s="19" t="inlineStr" r="L36">
@@ -2452,7 +2493,7 @@
       </c>
       <c s="19" t="inlineStr" r="K37">
         <is>
-          <t xml:space="preserve">SELECT</t>
+          <t xml:space="preserve">UPDATE</t>
         </is>
       </c>
       <c s="19" t="inlineStr" r="L37">
@@ -2495,7 +2536,7 @@
       </c>
       <c s="19" t="inlineStr" r="K38">
         <is>
-          <t xml:space="preserve">UPDATE</t>
+          <t xml:space="preserve">INSERT</t>
         </is>
       </c>
       <c s="19" t="inlineStr" r="L38">
@@ -2513,7 +2554,7 @@
       <c s="13" t="str" r="P38"/>
       <c s="19" t="inlineStr" r="Q38">
         <is>
-          <t xml:space="preserve">t1</t>
+          <t xml:space="preserve">t2</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R38">
@@ -2538,7 +2579,7 @@
       </c>
       <c s="19" t="inlineStr" r="K39">
         <is>
-          <t xml:space="preserve">INSERT</t>
+          <t xml:space="preserve">SELECT</t>
         </is>
       </c>
       <c s="19" t="inlineStr" r="L39">
@@ -2581,7 +2622,7 @@
       </c>
       <c s="19" t="inlineStr" r="K40">
         <is>
-          <t xml:space="preserve">SELECT</t>
+          <t xml:space="preserve">ALTER</t>
         </is>
       </c>
       <c s="19" t="inlineStr" r="L40">
@@ -2593,13 +2634,13 @@
       <c s="13" t="str" r="N40"/>
       <c s="19" t="inlineStr" r="O40">
         <is>
-          <t xml:space="preserve">dbo</t>
+          <t xml:space="preserve">TestSchema</t>
         </is>
       </c>
       <c s="13" t="str" r="P40"/>
       <c s="19" t="inlineStr" r="Q40">
         <is>
-          <t xml:space="preserve">t2</t>
+          <t xml:space="preserve">t1</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R40">
@@ -2624,7 +2665,7 @@
       </c>
       <c s="19" t="inlineStr" r="K41">
         <is>
-          <t xml:space="preserve">ALTER</t>
+          <t xml:space="preserve">DELETE</t>
         </is>
       </c>
       <c s="19" t="inlineStr" r="L41">
@@ -2654,7 +2695,7 @@
       <c s="12" t="str" r="T41"/>
       <c s="13" t="str" r="U41"/>
     </row>
-    <row r="42" ht="17" customHeight="0">
+    <row r="42" ht="17.05" customHeight="0">
       <c s="27" t="str" r="B42"/>
       <c s="28" t="str" r="D42"/>
       <c s="29" t="str" r="E42"/>
@@ -2667,7 +2708,7 @@
       </c>
       <c s="19" t="inlineStr" r="K42">
         <is>
-          <t xml:space="preserve">DELETE</t>
+          <t xml:space="preserve">INSERT</t>
         </is>
       </c>
       <c s="19" t="inlineStr" r="L42">
@@ -2697,7 +2738,7 @@
       <c s="12" t="str" r="T42"/>
       <c s="13" t="str" r="U42"/>
     </row>
-    <row r="43" ht="17.05" customHeight="0">
+    <row r="43" ht="17" customHeight="0">
       <c s="27" t="str" r="B43"/>
       <c s="28" t="str" r="D43"/>
       <c s="29" t="str" r="E43"/>
@@ -2710,7 +2751,7 @@
       </c>
       <c s="19" t="inlineStr" r="K43">
         <is>
-          <t xml:space="preserve">INSERT</t>
+          <t xml:space="preserve">SELECT</t>
         </is>
       </c>
       <c s="19" t="inlineStr" r="L43">
@@ -2753,7 +2794,7 @@
       </c>
       <c s="19" t="inlineStr" r="K44">
         <is>
-          <t xml:space="preserve">SELECT</t>
+          <t xml:space="preserve">UPDATE</t>
         </is>
       </c>
       <c s="19" t="inlineStr" r="L44">
@@ -2796,7 +2837,7 @@
       </c>
       <c s="19" t="inlineStr" r="K45">
         <is>
-          <t xml:space="preserve">UPDATE</t>
+          <t xml:space="preserve">ALTER</t>
         </is>
       </c>
       <c s="19" t="inlineStr" r="L45">
@@ -2814,7 +2855,7 @@
       <c s="13" t="str" r="P45"/>
       <c s="19" t="inlineStr" r="Q45">
         <is>
-          <t xml:space="preserve">t1</t>
+          <t xml:space="preserve">t2</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R45">
@@ -2839,7 +2880,7 @@
       </c>
       <c s="19" t="inlineStr" r="K46">
         <is>
-          <t xml:space="preserve">ALTER</t>
+          <t xml:space="preserve">INSERT</t>
         </is>
       </c>
       <c s="19" t="inlineStr" r="L46">
@@ -2872,9 +2913,11 @@
     <row r="47" ht="17" customHeight="0">
       <c s="27" t="str" r="B47"/>
       <c s="28" t="str" r="D47"/>
-      <c s="29" t="str" r="E47"/>
-      <c s="27" t="str" r="F47"/>
-      <c s="28" t="str" r="I47"/>
+      <c s="26" t="str" r="E47"/>
+      <c s="23" t="str" r="F47"/>
+      <c s="24" t="str" r="G47"/>
+      <c s="24" t="str" r="H47"/>
+      <c s="25" t="str" r="I47"/>
       <c s="19" t="inlineStr" r="J47">
         <is>
           <t xml:space="preserve">GRANT</t>
@@ -2882,7 +2925,7 @@
       </c>
       <c s="19" t="inlineStr" r="K47">
         <is>
-          <t xml:space="preserve">INSERT</t>
+          <t xml:space="preserve">SELECT</t>
         </is>
       </c>
       <c s="19" t="inlineStr" r="L47">
@@ -2912,14 +2955,22 @@
       <c s="12" t="str" r="T47"/>
       <c s="13" t="str" r="U47"/>
     </row>
-    <row r="48" ht="17" customHeight="0">
+    <row r="48" ht="17.05" customHeight="0">
       <c s="27" t="str" r="B48"/>
       <c s="28" t="str" r="D48"/>
-      <c s="26" t="str" r="E48"/>
-      <c s="23" t="str" r="F48"/>
-      <c s="24" t="str" r="G48"/>
-      <c s="24" t="str" r="H48"/>
-      <c s="25" t="str" r="I48"/>
+      <c s="19" t="inlineStr" r="E48">
+        <is>
+          <t xml:space="preserve">ro_Views</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="F48">
+        <is>
+          <t xml:space="preserve">SQL_USER</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="G48"/>
+      <c s="21" t="str" r="H48"/>
+      <c s="22" t="str" r="I48"/>
       <c s="19" t="inlineStr" r="J48">
         <is>
           <t xml:space="preserve">GRANT</t>
@@ -2932,20 +2983,20 @@
       </c>
       <c s="19" t="inlineStr" r="L48">
         <is>
-          <t xml:space="preserve">USER_TABLE</t>
+          <t xml:space="preserve">VIEW</t>
         </is>
       </c>
       <c s="12" t="str" r="M48"/>
       <c s="13" t="str" r="N48"/>
       <c s="19" t="inlineStr" r="O48">
         <is>
-          <t xml:space="preserve">TestSchema</t>
+          <t xml:space="preserve">dbo</t>
         </is>
       </c>
       <c s="13" t="str" r="P48"/>
       <c s="19" t="inlineStr" r="Q48">
         <is>
-          <t xml:space="preserve">t2</t>
+          <t xml:space="preserve">v1</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R48">
@@ -2957,22 +3008,12 @@
       <c s="12" t="str" r="T48"/>
       <c s="13" t="str" r="U48"/>
     </row>
-    <row r="49" ht="17.05" customHeight="0">
+    <row r="49" ht="17" customHeight="0">
       <c s="27" t="str" r="B49"/>
       <c s="28" t="str" r="D49"/>
-      <c s="19" t="inlineStr" r="E49">
-        <is>
-          <t xml:space="preserve">ro_Views</t>
-        </is>
-      </c>
-      <c s="19" t="inlineStr" r="F49">
-        <is>
-          <t xml:space="preserve">SQL_USER</t>
-        </is>
-      </c>
-      <c s="21" t="str" r="G49"/>
-      <c s="21" t="str" r="H49"/>
-      <c s="22" t="str" r="I49"/>
+      <c s="29" t="str" r="E49"/>
+      <c s="27" t="str" r="F49"/>
+      <c s="28" t="str" r="I49"/>
       <c s="19" t="inlineStr" r="J49">
         <is>
           <t xml:space="preserve">GRANT</t>
@@ -2998,7 +3039,7 @@
       <c s="13" t="str" r="P49"/>
       <c s="19" t="inlineStr" r="Q49">
         <is>
-          <t xml:space="preserve">v1</t>
+          <t xml:space="preserve">v2</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R49">
@@ -3035,18 +3076,18 @@
       <c s="13" t="str" r="N50"/>
       <c s="19" t="inlineStr" r="O50">
         <is>
-          <t xml:space="preserve">dbo</t>
+          <t xml:space="preserve">TestSchema</t>
         </is>
       </c>
       <c s="13" t="str" r="P50"/>
       <c s="19" t="inlineStr" r="Q50">
         <is>
-          <t xml:space="preserve">v2</t>
-        </is>
-      </c>
-      <c s="20" t="inlineStr" r="R50">
-        <is>
-          <t xml:space="preserve">*</t>
+          <t xml:space="preserve">v1</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="R50">
+        <is>
+          <t xml:space="preserve">s1</t>
         </is>
       </c>
       <c s="12" t="str" r="S50"/>
@@ -3054,11 +3095,14 @@
       <c s="13" t="str" r="U50"/>
     </row>
     <row r="51" ht="17" customHeight="0">
-      <c s="27" t="str" r="B51"/>
-      <c s="28" t="str" r="D51"/>
-      <c s="29" t="str" r="E51"/>
-      <c s="27" t="str" r="F51"/>
-      <c s="28" t="str" r="I51"/>
+      <c s="23" t="str" r="B51"/>
+      <c s="24" t="str" r="C51"/>
+      <c s="25" t="str" r="D51"/>
+      <c s="26" t="str" r="E51"/>
+      <c s="23" t="str" r="F51"/>
+      <c s="24" t="str" r="G51"/>
+      <c s="24" t="str" r="H51"/>
+      <c s="25" t="str" r="I51"/>
       <c s="19" t="inlineStr" r="J51">
         <is>
           <t xml:space="preserve">GRANT</t>
@@ -3084,12 +3128,12 @@
       <c s="13" t="str" r="P51"/>
       <c s="19" t="inlineStr" r="Q51">
         <is>
-          <t xml:space="preserve">v1</t>
+          <t xml:space="preserve">v2</t>
         </is>
       </c>
       <c s="19" t="inlineStr" r="R51">
         <is>
-          <t xml:space="preserve">s1</t>
+          <t xml:space="preserve">s2</t>
         </is>
       </c>
       <c s="12" t="str" r="S51"/>
@@ -3097,53 +3141,7 @@
       <c s="13" t="str" r="U51"/>
     </row>
     <row r="52" ht="17" customHeight="0">
-      <c s="23" t="str" r="B52"/>
-      <c s="24" t="str" r="C52"/>
-      <c s="25" t="str" r="D52"/>
-      <c s="26" t="str" r="E52"/>
-      <c s="23" t="str" r="F52"/>
-      <c s="24" t="str" r="G52"/>
-      <c s="24" t="str" r="H52"/>
-      <c s="25" t="str" r="I52"/>
-      <c s="19" t="inlineStr" r="J52">
-        <is>
-          <t xml:space="preserve">GRANT</t>
-        </is>
-      </c>
-      <c s="19" t="inlineStr" r="K52">
-        <is>
-          <t xml:space="preserve">SELECT</t>
-        </is>
-      </c>
-      <c s="19" t="inlineStr" r="L52">
-        <is>
-          <t xml:space="preserve">VIEW</t>
-        </is>
-      </c>
-      <c s="12" t="str" r="M52"/>
-      <c s="13" t="str" r="N52"/>
-      <c s="19" t="inlineStr" r="O52">
-        <is>
-          <t xml:space="preserve">TestSchema</t>
-        </is>
-      </c>
-      <c s="13" t="str" r="P52"/>
-      <c s="19" t="inlineStr" r="Q52">
-        <is>
-          <t xml:space="preserve">v2</t>
-        </is>
-      </c>
-      <c s="19" t="inlineStr" r="R52">
-        <is>
-          <t xml:space="preserve">s2</t>
-        </is>
-      </c>
-      <c s="12" t="str" r="S52"/>
-      <c s="12" t="str" r="T52"/>
-      <c s="13" t="str" r="U52"/>
-    </row>
-    <row r="53" ht="17" customHeight="0">
-      <c s="19" t="inlineStr" r="B53">
+      <c s="19" t="inlineStr" r="B52">
         <is>
           <r>
             <rPr>
@@ -3159,60 +3157,60 @@
           </r>
         </is>
       </c>
-      <c s="12" t="str" r="C53"/>
-      <c s="13" t="str" r="D53"/>
-      <c s="19" t="inlineStr" r="E53">
+      <c s="12" t="str" r="C52"/>
+      <c s="13" t="str" r="D52"/>
+      <c s="19" t="inlineStr" r="E52">
         <is>
           <t xml:space="preserve">db_execSPs</t>
         </is>
       </c>
-      <c s="19" t="inlineStr" r="F53">
+      <c s="19" t="inlineStr" r="F52">
         <is>
           <t xml:space="preserve">WINDOWS_USER</t>
         </is>
       </c>
-      <c s="12" t="str" r="G53"/>
-      <c s="12" t="str" r="H53"/>
-      <c s="13" t="str" r="I53"/>
-      <c s="19" t="inlineStr" r="J53">
-        <is>
-          <t xml:space="preserve">GRANT</t>
-        </is>
-      </c>
-      <c s="19" t="inlineStr" r="K53">
+      <c s="12" t="str" r="G52"/>
+      <c s="12" t="str" r="H52"/>
+      <c s="13" t="str" r="I52"/>
+      <c s="19" t="inlineStr" r="J52">
+        <is>
+          <t xml:space="preserve">GRANT</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K52">
         <is>
           <t xml:space="preserve">EXECUTE</t>
         </is>
       </c>
-      <c s="19" t="inlineStr" r="L53">
+      <c s="19" t="inlineStr" r="L52">
         <is>
           <t xml:space="preserve">DATABASE</t>
         </is>
       </c>
-      <c s="12" t="str" r="M53"/>
-      <c s="13" t="str" r="N53"/>
-      <c s="20" t="inlineStr" r="O53">
-        <is>
-          <t xml:space="preserve">*</t>
-        </is>
-      </c>
-      <c s="13" t="str" r="P53"/>
-      <c s="20" t="inlineStr" r="Q53">
-        <is>
-          <t xml:space="preserve">*</t>
-        </is>
-      </c>
-      <c s="20" t="inlineStr" r="R53">
-        <is>
-          <t xml:space="preserve">*</t>
-        </is>
-      </c>
-      <c s="12" t="str" r="S53"/>
-      <c s="12" t="str" r="T53"/>
-      <c s="13" t="str" r="U53"/>
-    </row>
-    <row r="54" ht="17" customHeight="0">
-      <c s="19" t="inlineStr" r="B54">
+      <c s="12" t="str" r="M52"/>
+      <c s="13" t="str" r="N52"/>
+      <c s="20" t="inlineStr" r="O52">
+        <is>
+          <t xml:space="preserve">*</t>
+        </is>
+      </c>
+      <c s="13" t="str" r="P52"/>
+      <c s="20" t="inlineStr" r="Q52">
+        <is>
+          <t xml:space="preserve">*</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="R52">
+        <is>
+          <t xml:space="preserve">*</t>
+        </is>
+      </c>
+      <c s="12" t="str" r="S52"/>
+      <c s="12" t="str" r="T52"/>
+      <c s="13" t="str" r="U52"/>
+    </row>
+    <row r="53" ht="17" customHeight="0">
+      <c s="19" t="inlineStr" r="B53">
         <is>
           <r>
             <rPr>
@@ -3228,17 +3226,60 @@
           </r>
         </is>
       </c>
-      <c s="21" t="str" r="C54"/>
-      <c s="22" t="str" r="D54"/>
-      <c s="19" t="str" r="E54"/>
-      <c s="19" t="inlineStr" r="F54">
+      <c s="21" t="str" r="C53"/>
+      <c s="22" t="str" r="D53"/>
+      <c s="19" t="str" r="E53"/>
+      <c s="19" t="inlineStr" r="F53">
         <is>
           <t xml:space="preserve">DATABASE_ROLE</t>
         </is>
       </c>
-      <c s="21" t="str" r="G54"/>
-      <c s="21" t="str" r="H54"/>
-      <c s="22" t="str" r="I54"/>
+      <c s="21" t="str" r="G53"/>
+      <c s="21" t="str" r="H53"/>
+      <c s="22" t="str" r="I53"/>
+      <c s="19" t="inlineStr" r="J53">
+        <is>
+          <t xml:space="preserve">GRANT</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K53">
+        <is>
+          <t xml:space="preserve">SELECT</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="L53">
+        <is>
+          <t xml:space="preserve">DATABASE</t>
+        </is>
+      </c>
+      <c s="12" t="str" r="M53"/>
+      <c s="13" t="str" r="N53"/>
+      <c s="20" t="inlineStr" r="O53">
+        <is>
+          <t xml:space="preserve">*</t>
+        </is>
+      </c>
+      <c s="13" t="str" r="P53"/>
+      <c s="20" t="inlineStr" r="Q53">
+        <is>
+          <t xml:space="preserve">*</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="R53">
+        <is>
+          <t xml:space="preserve">*</t>
+        </is>
+      </c>
+      <c s="12" t="str" r="S53"/>
+      <c s="12" t="str" r="T53"/>
+      <c s="13" t="str" r="U53"/>
+    </row>
+    <row r="54" ht="17.05" customHeight="0">
+      <c s="27" t="str" r="B54"/>
+      <c s="28" t="str" r="D54"/>
+      <c s="29" t="str" r="E54"/>
+      <c s="27" t="str" r="F54"/>
+      <c s="28" t="str" r="I54"/>
       <c s="19" t="inlineStr" r="J54">
         <is>
           <t xml:space="preserve">GRANT</t>
@@ -3246,7 +3287,7 @@
       </c>
       <c s="19" t="inlineStr" r="K54">
         <is>
-          <t xml:space="preserve">SELECT</t>
+          <t xml:space="preserve">VIEW ANY COLUMN MASTER KEY DEFINITION</t>
         </is>
       </c>
       <c s="19" t="inlineStr" r="L54">
@@ -3276,7 +3317,7 @@
       <c s="12" t="str" r="T54"/>
       <c s="13" t="str" r="U54"/>
     </row>
-    <row r="55" ht="17.05" customHeight="0">
+    <row r="55" ht="17" customHeight="0">
       <c s="27" t="str" r="B55"/>
       <c s="28" t="str" r="D55"/>
       <c s="29" t="str" r="E55"/>
@@ -3289,25 +3330,25 @@
       </c>
       <c s="19" t="inlineStr" r="K55">
         <is>
-          <t xml:space="preserve">VIEW ANY COLUMN MASTER KEY DEFINITION</t>
+          <t xml:space="preserve">SELECT</t>
         </is>
       </c>
       <c s="19" t="inlineStr" r="L55">
         <is>
-          <t xml:space="preserve">DATABASE</t>
+          <t xml:space="preserve">VIEW</t>
         </is>
       </c>
       <c s="12" t="str" r="M55"/>
       <c s="13" t="str" r="N55"/>
-      <c s="20" t="inlineStr" r="O55">
-        <is>
-          <t xml:space="preserve">*</t>
+      <c s="19" t="inlineStr" r="O55">
+        <is>
+          <t xml:space="preserve">sys</t>
         </is>
       </c>
       <c s="13" t="str" r="P55"/>
-      <c s="20" t="inlineStr" r="Q55">
-        <is>
-          <t xml:space="preserve">*</t>
+      <c s="19" t="inlineStr" r="Q55">
+        <is>
+          <t xml:space="preserve">all_columns</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R55">
@@ -3350,7 +3391,7 @@
       <c s="13" t="str" r="P56"/>
       <c s="19" t="inlineStr" r="Q56">
         <is>
-          <t xml:space="preserve">all_columns</t>
+          <t xml:space="preserve">all_objects</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R56">
@@ -3393,7 +3434,7 @@
       <c s="13" t="str" r="P57"/>
       <c s="19" t="inlineStr" r="Q57">
         <is>
-          <t xml:space="preserve">all_objects</t>
+          <t xml:space="preserve">all_parameters</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R57">
@@ -3436,7 +3477,7 @@
       <c s="13" t="str" r="P58"/>
       <c s="19" t="inlineStr" r="Q58">
         <is>
-          <t xml:space="preserve">all_parameters</t>
+          <t xml:space="preserve">all_sql_modules</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R58">
@@ -3479,7 +3520,7 @@
       <c s="13" t="str" r="P59"/>
       <c s="19" t="inlineStr" r="Q59">
         <is>
-          <t xml:space="preserve">all_sql_modules</t>
+          <t xml:space="preserve">all_views</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R59">
@@ -3522,7 +3563,7 @@
       <c s="13" t="str" r="P60"/>
       <c s="19" t="inlineStr" r="Q60">
         <is>
-          <t xml:space="preserve">all_views</t>
+          <t xml:space="preserve">allocation_units</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R60">
@@ -3534,7 +3575,7 @@
       <c s="12" t="str" r="T60"/>
       <c s="13" t="str" r="U60"/>
     </row>
-    <row r="61" ht="17" customHeight="0">
+    <row r="61" ht="17.05" customHeight="0">
       <c s="27" t="str" r="B61"/>
       <c s="28" t="str" r="D61"/>
       <c s="29" t="str" r="E61"/>
@@ -3565,7 +3606,7 @@
       <c s="13" t="str" r="P61"/>
       <c s="19" t="inlineStr" r="Q61">
         <is>
-          <t xml:space="preserve">allocation_units</t>
+          <t xml:space="preserve">assemblies</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R61">
@@ -3577,7 +3618,7 @@
       <c s="12" t="str" r="T61"/>
       <c s="13" t="str" r="U61"/>
     </row>
-    <row r="62" ht="17.05" customHeight="0">
+    <row r="62" ht="17" customHeight="0">
       <c s="27" t="str" r="B62"/>
       <c s="28" t="str" r="D62"/>
       <c s="29" t="str" r="E62"/>
@@ -3608,7 +3649,7 @@
       <c s="13" t="str" r="P62"/>
       <c s="19" t="inlineStr" r="Q62">
         <is>
-          <t xml:space="preserve">assemblies</t>
+          <t xml:space="preserve">assembly_files</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R62">
@@ -3651,7 +3692,7 @@
       <c s="13" t="str" r="P63"/>
       <c s="19" t="inlineStr" r="Q63">
         <is>
-          <t xml:space="preserve">assembly_files</t>
+          <t xml:space="preserve">assembly_modules</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R63">
@@ -3694,7 +3735,7 @@
       <c s="13" t="str" r="P64"/>
       <c s="19" t="inlineStr" r="Q64">
         <is>
-          <t xml:space="preserve">assembly_modules</t>
+          <t xml:space="preserve">assembly_references</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R64">
@@ -3737,7 +3778,7 @@
       <c s="13" t="str" r="P65"/>
       <c s="19" t="inlineStr" r="Q65">
         <is>
-          <t xml:space="preserve">assembly_references</t>
+          <t xml:space="preserve">assembly_types</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R65">
@@ -3780,7 +3821,7 @@
       <c s="13" t="str" r="P66"/>
       <c s="19" t="inlineStr" r="Q66">
         <is>
-          <t xml:space="preserve">assembly_types</t>
+          <t xml:space="preserve">asymmetric_keys</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R66">
@@ -3792,7 +3833,7 @@
       <c s="12" t="str" r="T66"/>
       <c s="13" t="str" r="U66"/>
     </row>
-    <row r="67" ht="17" customHeight="0">
+    <row r="67" ht="17.05" customHeight="0">
       <c s="27" t="str" r="B67"/>
       <c s="28" t="str" r="D67"/>
       <c s="29" t="str" r="E67"/>
@@ -3823,7 +3864,7 @@
       <c s="13" t="str" r="P67"/>
       <c s="19" t="inlineStr" r="Q67">
         <is>
-          <t xml:space="preserve">asymmetric_keys</t>
+          <t xml:space="preserve">certificates</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R67">
@@ -3835,7 +3876,7 @@
       <c s="12" t="str" r="T67"/>
       <c s="13" t="str" r="U67"/>
     </row>
-    <row r="68" ht="17.05" customHeight="0">
+    <row r="68" ht="17" customHeight="0">
       <c s="27" t="str" r="B68"/>
       <c s="28" t="str" r="D68"/>
       <c s="29" t="str" r="E68"/>
@@ -3866,7 +3907,7 @@
       <c s="13" t="str" r="P68"/>
       <c s="19" t="inlineStr" r="Q68">
         <is>
-          <t xml:space="preserve">certificates</t>
+          <t xml:space="preserve">change_tracking_tables</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R68">
@@ -3909,7 +3950,7 @@
       <c s="13" t="str" r="P69"/>
       <c s="19" t="inlineStr" r="Q69">
         <is>
-          <t xml:space="preserve">change_tracking_tables</t>
+          <t xml:space="preserve">check_constraints</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R69">
@@ -3952,7 +3993,7 @@
       <c s="13" t="str" r="P70"/>
       <c s="19" t="inlineStr" r="Q70">
         <is>
-          <t xml:space="preserve">check_constraints</t>
+          <t xml:space="preserve">column_encryption_key_values</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R70">
@@ -3995,7 +4036,7 @@
       <c s="13" t="str" r="P71"/>
       <c s="19" t="inlineStr" r="Q71">
         <is>
-          <t xml:space="preserve">column_encryption_key_values</t>
+          <t xml:space="preserve">column_encryption_keys</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R71">
@@ -4038,7 +4079,7 @@
       <c s="13" t="str" r="P72"/>
       <c s="19" t="inlineStr" r="Q72">
         <is>
-          <t xml:space="preserve">column_encryption_keys</t>
+          <t xml:space="preserve">column_master_keys</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R72">
@@ -4050,7 +4091,7 @@
       <c s="12" t="str" r="T72"/>
       <c s="13" t="str" r="U72"/>
     </row>
-    <row r="73" ht="17" customHeight="0">
+    <row r="73" ht="17.05" customHeight="0">
       <c s="27" t="str" r="B73"/>
       <c s="28" t="str" r="D73"/>
       <c s="29" t="str" r="E73"/>
@@ -4081,7 +4122,7 @@
       <c s="13" t="str" r="P73"/>
       <c s="19" t="inlineStr" r="Q73">
         <is>
-          <t xml:space="preserve">column_master_keys</t>
+          <t xml:space="preserve">column_store_dictionaries</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R73">
@@ -4093,7 +4134,7 @@
       <c s="12" t="str" r="T73"/>
       <c s="13" t="str" r="U73"/>
     </row>
-    <row r="74" ht="17.05" customHeight="0">
+    <row r="74" ht="17" customHeight="0">
       <c s="27" t="str" r="B74"/>
       <c s="28" t="str" r="D74"/>
       <c s="29" t="str" r="E74"/>
@@ -4124,7 +4165,7 @@
       <c s="13" t="str" r="P74"/>
       <c s="19" t="inlineStr" r="Q74">
         <is>
-          <t xml:space="preserve">column_store_dictionaries</t>
+          <t xml:space="preserve">column_store_row_groups</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R74">
@@ -4167,7 +4208,7 @@
       <c s="13" t="str" r="P75"/>
       <c s="19" t="inlineStr" r="Q75">
         <is>
-          <t xml:space="preserve">column_store_row_groups</t>
+          <t xml:space="preserve">column_store_segments</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R75">
@@ -4210,7 +4251,7 @@
       <c s="13" t="str" r="P76"/>
       <c s="19" t="inlineStr" r="Q76">
         <is>
-          <t xml:space="preserve">column_store_segments</t>
+          <t xml:space="preserve">column_type_usages</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R76">
@@ -4253,7 +4294,7 @@
       <c s="13" t="str" r="P77"/>
       <c s="19" t="inlineStr" r="Q77">
         <is>
-          <t xml:space="preserve">column_type_usages</t>
+          <t xml:space="preserve">column_xml_schema_collection_usages</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R77">
@@ -4296,7 +4337,7 @@
       <c s="13" t="str" r="P78"/>
       <c s="19" t="inlineStr" r="Q78">
         <is>
-          <t xml:space="preserve">column_xml_schema_collection_usages</t>
+          <t xml:space="preserve">columns</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R78">
@@ -4339,7 +4380,7 @@
       <c s="13" t="str" r="P79"/>
       <c s="19" t="inlineStr" r="Q79">
         <is>
-          <t xml:space="preserve">columns</t>
+          <t xml:space="preserve">computed_columns</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R79">
@@ -4351,7 +4392,7 @@
       <c s="12" t="str" r="T79"/>
       <c s="13" t="str" r="U79"/>
     </row>
-    <row r="80" ht="17" customHeight="0">
+    <row r="80" ht="17.05" customHeight="0">
       <c s="27" t="str" r="B80"/>
       <c s="28" t="str" r="D80"/>
       <c s="29" t="str" r="E80"/>
@@ -4382,7 +4423,7 @@
       <c s="13" t="str" r="P80"/>
       <c s="19" t="inlineStr" r="Q80">
         <is>
-          <t xml:space="preserve">computed_columns</t>
+          <t xml:space="preserve">conversation_endpoints</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R80">
@@ -4394,7 +4435,7 @@
       <c s="12" t="str" r="T80"/>
       <c s="13" t="str" r="U80"/>
     </row>
-    <row r="81" ht="17.05" customHeight="0">
+    <row r="81" ht="17" customHeight="0">
       <c s="27" t="str" r="B81"/>
       <c s="28" t="str" r="D81"/>
       <c s="29" t="str" r="E81"/>
@@ -4425,7 +4466,7 @@
       <c s="13" t="str" r="P81"/>
       <c s="19" t="inlineStr" r="Q81">
         <is>
-          <t xml:space="preserve">conversation_endpoints</t>
+          <t xml:space="preserve">conversation_groups</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R81">
@@ -4468,7 +4509,7 @@
       <c s="13" t="str" r="P82"/>
       <c s="19" t="inlineStr" r="Q82">
         <is>
-          <t xml:space="preserve">conversation_groups</t>
+          <t xml:space="preserve">conversation_priorities</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R82">
@@ -4511,7 +4552,7 @@
       <c s="13" t="str" r="P83"/>
       <c s="19" t="inlineStr" r="Q83">
         <is>
-          <t xml:space="preserve">conversation_priorities</t>
+          <t xml:space="preserve">crypt_properties</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R83">
@@ -4554,7 +4595,7 @@
       <c s="13" t="str" r="P84"/>
       <c s="19" t="inlineStr" r="Q84">
         <is>
-          <t xml:space="preserve">crypt_properties</t>
+          <t xml:space="preserve">data_spaces</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R84">
@@ -4597,7 +4638,7 @@
       <c s="13" t="str" r="P85"/>
       <c s="19" t="inlineStr" r="Q85">
         <is>
-          <t xml:space="preserve">data_spaces</t>
+          <t xml:space="preserve">database_audit_specification_details</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R85">
@@ -4609,7 +4650,7 @@
       <c s="12" t="str" r="T85"/>
       <c s="13" t="str" r="U85"/>
     </row>
-    <row r="86" ht="17" customHeight="0">
+    <row r="86" ht="17.05" customHeight="0">
       <c s="27" t="str" r="B86"/>
       <c s="28" t="str" r="D86"/>
       <c s="29" t="str" r="E86"/>
@@ -4640,7 +4681,7 @@
       <c s="13" t="str" r="P86"/>
       <c s="19" t="inlineStr" r="Q86">
         <is>
-          <t xml:space="preserve">database_audit_specification_details</t>
+          <t xml:space="preserve">database_audit_specifications</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R86">
@@ -4652,7 +4693,7 @@
       <c s="12" t="str" r="T86"/>
       <c s="13" t="str" r="U86"/>
     </row>
-    <row r="87" ht="17.05" customHeight="0">
+    <row r="87" ht="17" customHeight="0">
       <c s="27" t="str" r="B87"/>
       <c s="28" t="str" r="D87"/>
       <c s="29" t="str" r="E87"/>
@@ -4683,7 +4724,7 @@
       <c s="13" t="str" r="P87"/>
       <c s="19" t="inlineStr" r="Q87">
         <is>
-          <t xml:space="preserve">database_audit_specifications</t>
+          <t xml:space="preserve">database_automatic_tuning_configurations</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R87">
@@ -4726,7 +4767,7 @@
       <c s="13" t="str" r="P88"/>
       <c s="19" t="inlineStr" r="Q88">
         <is>
-          <t xml:space="preserve">database_automatic_tuning_configurations</t>
+          <t xml:space="preserve">database_automatic_tuning_mode</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R88">
@@ -4769,7 +4810,7 @@
       <c s="13" t="str" r="P89"/>
       <c s="19" t="inlineStr" r="Q89">
         <is>
-          <t xml:space="preserve">database_automatic_tuning_mode</t>
+          <t xml:space="preserve">database_automatic_tuning_options</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R89">
@@ -4812,7 +4853,7 @@
       <c s="13" t="str" r="P90"/>
       <c s="19" t="inlineStr" r="Q90">
         <is>
-          <t xml:space="preserve">database_automatic_tuning_options</t>
+          <t xml:space="preserve">database_credentials</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R90">
@@ -4855,7 +4896,7 @@
       <c s="13" t="str" r="P91"/>
       <c s="19" t="inlineStr" r="Q91">
         <is>
-          <t xml:space="preserve">database_credentials</t>
+          <t xml:space="preserve">database_files</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R91">
@@ -4898,7 +4939,7 @@
       <c s="13" t="str" r="P92"/>
       <c s="19" t="inlineStr" r="Q92">
         <is>
-          <t xml:space="preserve">database_files</t>
+          <t xml:space="preserve">database_ledger_blocks</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R92">
@@ -4910,7 +4951,7 @@
       <c s="12" t="str" r="T92"/>
       <c s="13" t="str" r="U92"/>
     </row>
-    <row r="93" ht="17" customHeight="0">
+    <row r="93" ht="17.05" customHeight="0">
       <c s="27" t="str" r="B93"/>
       <c s="28" t="str" r="D93"/>
       <c s="29" t="str" r="E93"/>
@@ -4941,7 +4982,7 @@
       <c s="13" t="str" r="P93"/>
       <c s="19" t="inlineStr" r="Q93">
         <is>
-          <t xml:space="preserve">database_ledger_blocks</t>
+          <t xml:space="preserve">database_ledger_digest_locations</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R93">
@@ -4953,7 +4994,7 @@
       <c s="12" t="str" r="T93"/>
       <c s="13" t="str" r="U93"/>
     </row>
-    <row r="94" ht="17.05" customHeight="0">
+    <row r="94" ht="17" customHeight="0">
       <c s="27" t="str" r="B94"/>
       <c s="28" t="str" r="D94"/>
       <c s="29" t="str" r="E94"/>
@@ -4984,7 +5025,7 @@
       <c s="13" t="str" r="P94"/>
       <c s="19" t="inlineStr" r="Q94">
         <is>
-          <t xml:space="preserve">database_ledger_digest_locations</t>
+          <t xml:space="preserve">database_ledger_transactions</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R94">
@@ -5027,7 +5068,7 @@
       <c s="13" t="str" r="P95"/>
       <c s="19" t="inlineStr" r="Q95">
         <is>
-          <t xml:space="preserve">database_ledger_transactions</t>
+          <t xml:space="preserve">database_permissions</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R95">
@@ -5070,7 +5111,7 @@
       <c s="13" t="str" r="P96"/>
       <c s="19" t="inlineStr" r="Q96">
         <is>
-          <t xml:space="preserve">database_permissions</t>
+          <t xml:space="preserve">database_principals</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R96">
@@ -5113,7 +5154,7 @@
       <c s="13" t="str" r="P97"/>
       <c s="19" t="inlineStr" r="Q97">
         <is>
-          <t xml:space="preserve">database_principals</t>
+          <t xml:space="preserve">database_role_members</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R97">
@@ -5156,7 +5197,7 @@
       <c s="13" t="str" r="P98"/>
       <c s="19" t="inlineStr" r="Q98">
         <is>
-          <t xml:space="preserve">database_role_members</t>
+          <t xml:space="preserve">database_scoped_configurations</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R98">
@@ -5168,7 +5209,7 @@
       <c s="12" t="str" r="T98"/>
       <c s="13" t="str" r="U98"/>
     </row>
-    <row r="99" ht="17" customHeight="0">
+    <row r="99" ht="17.05" customHeight="0">
       <c s="27" t="str" r="B99"/>
       <c s="28" t="str" r="D99"/>
       <c s="29" t="str" r="E99"/>
@@ -5199,7 +5240,7 @@
       <c s="13" t="str" r="P99"/>
       <c s="19" t="inlineStr" r="Q99">
         <is>
-          <t xml:space="preserve">database_scoped_configurations</t>
+          <t xml:space="preserve">database_scoped_credentials</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R99">
@@ -5211,7 +5252,7 @@
       <c s="12" t="str" r="T99"/>
       <c s="13" t="str" r="U99"/>
     </row>
-    <row r="100" ht="17.05" customHeight="0">
+    <row r="100" ht="17" customHeight="0">
       <c s="27" t="str" r="B100"/>
       <c s="28" t="str" r="D100"/>
       <c s="29" t="str" r="E100"/>
@@ -5242,7 +5283,7 @@
       <c s="13" t="str" r="P100"/>
       <c s="19" t="inlineStr" r="Q100">
         <is>
-          <t xml:space="preserve">database_scoped_credentials</t>
+          <t xml:space="preserve">default_constraints</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R100">
@@ -5285,7 +5326,7 @@
       <c s="13" t="str" r="P101"/>
       <c s="19" t="inlineStr" r="Q101">
         <is>
-          <t xml:space="preserve">default_constraints</t>
+          <t xml:space="preserve">destination_data_spaces</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R101">
@@ -5328,7 +5369,7 @@
       <c s="13" t="str" r="P102"/>
       <c s="19" t="inlineStr" r="Q102">
         <is>
-          <t xml:space="preserve">destination_data_spaces</t>
+          <t xml:space="preserve">dm_db_column_store_row_group_physical_stats</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R102">
@@ -5371,7 +5412,7 @@
       <c s="13" t="str" r="P103"/>
       <c s="19" t="inlineStr" r="Q103">
         <is>
-          <t xml:space="preserve">dm_db_column_store_row_group_physical_stats</t>
+          <t xml:space="preserve">dm_distributed_exchange_stats</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R103">
@@ -5414,7 +5455,7 @@
       <c s="13" t="str" r="P104"/>
       <c s="19" t="inlineStr" r="Q104">
         <is>
-          <t xml:space="preserve">dm_distributed_exchange_stats</t>
+          <t xml:space="preserve">dm_external_provider_certificate_info</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R104">
@@ -5426,7 +5467,7 @@
       <c s="12" t="str" r="T104"/>
       <c s="13" t="str" r="U104"/>
     </row>
-    <row r="105" ht="17" customHeight="0">
+    <row r="105" ht="17.05" customHeight="0">
       <c s="27" t="str" r="B105"/>
       <c s="28" t="str" r="D105"/>
       <c s="29" t="str" r="E105"/>
@@ -5457,7 +5498,7 @@
       <c s="13" t="str" r="P105"/>
       <c s="19" t="inlineStr" r="Q105">
         <is>
-          <t xml:space="preserve">dm_external_provider_certificate_info</t>
+          <t xml:space="preserve">edge_constraint_clauses</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R105">
@@ -5469,7 +5510,7 @@
       <c s="12" t="str" r="T105"/>
       <c s="13" t="str" r="U105"/>
     </row>
-    <row r="106" ht="17.05" customHeight="0">
+    <row r="106" ht="17" customHeight="0">
       <c s="27" t="str" r="B106"/>
       <c s="28" t="str" r="D106"/>
       <c s="29" t="str" r="E106"/>
@@ -5500,7 +5541,7 @@
       <c s="13" t="str" r="P106"/>
       <c s="19" t="inlineStr" r="Q106">
         <is>
-          <t xml:space="preserve">edge_constraint_clauses</t>
+          <t xml:space="preserve">edge_constraints</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R106">
@@ -5543,7 +5584,7 @@
       <c s="13" t="str" r="P107"/>
       <c s="19" t="inlineStr" r="Q107">
         <is>
-          <t xml:space="preserve">edge_constraints</t>
+          <t xml:space="preserve">event_notifications</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R107">
@@ -5586,7 +5627,7 @@
       <c s="13" t="str" r="P108"/>
       <c s="19" t="inlineStr" r="Q108">
         <is>
-          <t xml:space="preserve">event_notifications</t>
+          <t xml:space="preserve">events</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R108">
@@ -5629,7 +5670,7 @@
       <c s="13" t="str" r="P109"/>
       <c s="19" t="inlineStr" r="Q109">
         <is>
-          <t xml:space="preserve">events</t>
+          <t xml:space="preserve">extended_procedures</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R109">
@@ -5672,7 +5713,7 @@
       <c s="13" t="str" r="P110"/>
       <c s="19" t="inlineStr" r="Q110">
         <is>
-          <t xml:space="preserve">extended_procedures</t>
+          <t xml:space="preserve">extended_properties</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R110">
@@ -5715,7 +5756,7 @@
       <c s="13" t="str" r="P111"/>
       <c s="19" t="inlineStr" r="Q111">
         <is>
-          <t xml:space="preserve">extended_properties</t>
+          <t xml:space="preserve">external_data_sources</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R111">
@@ -5727,7 +5768,7 @@
       <c s="12" t="str" r="T111"/>
       <c s="13" t="str" r="U111"/>
     </row>
-    <row r="112" ht="17" customHeight="0">
+    <row r="112" ht="17.05" customHeight="0">
       <c s="27" t="str" r="B112"/>
       <c s="28" t="str" r="D112"/>
       <c s="29" t="str" r="E112"/>
@@ -5758,7 +5799,7 @@
       <c s="13" t="str" r="P112"/>
       <c s="19" t="inlineStr" r="Q112">
         <is>
-          <t xml:space="preserve">external_data_sources</t>
+          <t xml:space="preserve">external_file_formats</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R112">
@@ -5770,7 +5811,7 @@
       <c s="12" t="str" r="T112"/>
       <c s="13" t="str" r="U112"/>
     </row>
-    <row r="113" ht="17.05" customHeight="0">
+    <row r="113" ht="17" customHeight="0">
       <c s="27" t="str" r="B113"/>
       <c s="28" t="str" r="D113"/>
       <c s="29" t="str" r="E113"/>
@@ -5801,7 +5842,7 @@
       <c s="13" t="str" r="P113"/>
       <c s="19" t="inlineStr" r="Q113">
         <is>
-          <t xml:space="preserve">external_file_formats</t>
+          <t xml:space="preserve">external_governance_classification_attributes</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R113">
@@ -5844,7 +5885,7 @@
       <c s="13" t="str" r="P114"/>
       <c s="19" t="inlineStr" r="Q114">
         <is>
-          <t xml:space="preserve">external_governance_classification_attributes</t>
+          <t xml:space="preserve">external_governance_classifications</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R114">
@@ -5887,7 +5928,7 @@
       <c s="13" t="str" r="P115"/>
       <c s="19" t="inlineStr" r="Q115">
         <is>
-          <t xml:space="preserve">external_governance_classifications</t>
+          <t xml:space="preserve">external_governance_classifications_mapping</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R115">
@@ -5930,7 +5971,7 @@
       <c s="13" t="str" r="P116"/>
       <c s="19" t="inlineStr" r="Q116">
         <is>
-          <t xml:space="preserve">external_governance_classifications_mapping</t>
+          <t xml:space="preserve">external_governance_sensitivity_classifications</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R116">
@@ -5973,7 +6014,7 @@
       <c s="13" t="str" r="P117"/>
       <c s="19" t="inlineStr" r="Q117">
         <is>
-          <t xml:space="preserve">external_governance_sensitivity_classifications</t>
+          <t xml:space="preserve">external_governance_sensitivity_labels</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R117">
@@ -5985,7 +6026,7 @@
       <c s="12" t="str" r="T117"/>
       <c s="13" t="str" r="U117"/>
     </row>
-    <row r="118" ht="17" customHeight="0">
+    <row r="118" ht="17.05" customHeight="0">
       <c s="27" t="str" r="B118"/>
       <c s="28" t="str" r="D118"/>
       <c s="29" t="str" r="E118"/>
@@ -6016,7 +6057,7 @@
       <c s="13" t="str" r="P118"/>
       <c s="19" t="inlineStr" r="Q118">
         <is>
-          <t xml:space="preserve">external_governance_sensitivity_labels</t>
+          <t xml:space="preserve">external_governance_sensitivity_labels_mapping</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R118">
@@ -6028,7 +6069,7 @@
       <c s="12" t="str" r="T118"/>
       <c s="13" t="str" r="U118"/>
     </row>
-    <row r="119" ht="17.05" customHeight="0">
+    <row r="119" ht="17" customHeight="0">
       <c s="27" t="str" r="B119"/>
       <c s="28" t="str" r="D119"/>
       <c s="29" t="str" r="E119"/>
@@ -6059,7 +6100,7 @@
       <c s="13" t="str" r="P119"/>
       <c s="19" t="inlineStr" r="Q119">
         <is>
-          <t xml:space="preserve">external_governance_sensitivity_labels_mapping</t>
+          <t xml:space="preserve">external_job_streams</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R119">
@@ -6102,7 +6143,7 @@
       <c s="13" t="str" r="P120"/>
       <c s="19" t="inlineStr" r="Q120">
         <is>
-          <t xml:space="preserve">external_job_streams</t>
+          <t xml:space="preserve">external_language_files</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R120">
@@ -6145,7 +6186,7 @@
       <c s="13" t="str" r="P121"/>
       <c s="19" t="inlineStr" r="Q121">
         <is>
-          <t xml:space="preserve">external_language_files</t>
+          <t xml:space="preserve">external_languages</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R121">
@@ -6188,7 +6229,7 @@
       <c s="13" t="str" r="P122"/>
       <c s="19" t="inlineStr" r="Q122">
         <is>
-          <t xml:space="preserve">external_languages</t>
+          <t xml:space="preserve">external_libraries</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R122">
@@ -6231,7 +6272,7 @@
       <c s="13" t="str" r="P123"/>
       <c s="19" t="inlineStr" r="Q123">
         <is>
-          <t xml:space="preserve">external_libraries</t>
+          <t xml:space="preserve">external_libraries_installed</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R123">
@@ -6243,7 +6284,7 @@
       <c s="12" t="str" r="T123"/>
       <c s="13" t="str" r="U123"/>
     </row>
-    <row r="124" ht="17" customHeight="0">
+    <row r="124" ht="17.05" customHeight="0">
       <c s="27" t="str" r="B124"/>
       <c s="28" t="str" r="D124"/>
       <c s="29" t="str" r="E124"/>
@@ -6274,7 +6315,7 @@
       <c s="13" t="str" r="P124"/>
       <c s="19" t="inlineStr" r="Q124">
         <is>
-          <t xml:space="preserve">external_libraries_installed</t>
+          <t xml:space="preserve">external_library_files</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R124">
@@ -6286,7 +6327,7 @@
       <c s="12" t="str" r="T124"/>
       <c s="13" t="str" r="U124"/>
     </row>
-    <row r="125" ht="17.05" customHeight="0">
+    <row r="125" ht="17" customHeight="0">
       <c s="27" t="str" r="B125"/>
       <c s="28" t="str" r="D125"/>
       <c s="29" t="str" r="E125"/>
@@ -6317,7 +6358,7 @@
       <c s="13" t="str" r="P125"/>
       <c s="19" t="inlineStr" r="Q125">
         <is>
-          <t xml:space="preserve">external_library_files</t>
+          <t xml:space="preserve">external_library_setup_errors</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R125">
@@ -6360,7 +6401,7 @@
       <c s="13" t="str" r="P126"/>
       <c s="19" t="inlineStr" r="Q126">
         <is>
-          <t xml:space="preserve">external_library_setup_errors</t>
+          <t xml:space="preserve">external_stream_columns</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R126">
@@ -6403,7 +6444,7 @@
       <c s="13" t="str" r="P127"/>
       <c s="19" t="inlineStr" r="Q127">
         <is>
-          <t xml:space="preserve">external_stream_columns</t>
+          <t xml:space="preserve">external_streaming_jobs</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R127">
@@ -6446,7 +6487,7 @@
       <c s="13" t="str" r="P128"/>
       <c s="19" t="inlineStr" r="Q128">
         <is>
-          <t xml:space="preserve">external_streaming_jobs</t>
+          <t xml:space="preserve">external_streams</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R128">
@@ -6489,7 +6530,7 @@
       <c s="13" t="str" r="P129"/>
       <c s="19" t="inlineStr" r="Q129">
         <is>
-          <t xml:space="preserve">external_streams</t>
+          <t xml:space="preserve">external_table_columns</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R129">
@@ -6532,7 +6573,7 @@
       <c s="13" t="str" r="P130"/>
       <c s="19" t="inlineStr" r="Q130">
         <is>
-          <t xml:space="preserve">external_table_columns</t>
+          <t xml:space="preserve">external_table_partitioning_columns</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R130">
@@ -6544,7 +6585,7 @@
       <c s="12" t="str" r="T130"/>
       <c s="13" t="str" r="U130"/>
     </row>
-    <row r="131" ht="17" customHeight="0">
+    <row r="131" ht="17.05" customHeight="0">
       <c s="27" t="str" r="B131"/>
       <c s="28" t="str" r="D131"/>
       <c s="29" t="str" r="E131"/>
@@ -6575,7 +6616,7 @@
       <c s="13" t="str" r="P131"/>
       <c s="19" t="inlineStr" r="Q131">
         <is>
-          <t xml:space="preserve">external_table_partitioning_columns</t>
+          <t xml:space="preserve">external_tables</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R131">
@@ -6587,7 +6628,7 @@
       <c s="12" t="str" r="T131"/>
       <c s="13" t="str" r="U131"/>
     </row>
-    <row r="132" ht="17.05" customHeight="0">
+    <row r="132" ht="17" customHeight="0">
       <c s="27" t="str" r="B132"/>
       <c s="28" t="str" r="D132"/>
       <c s="29" t="str" r="E132"/>
@@ -6618,7 +6659,7 @@
       <c s="13" t="str" r="P132"/>
       <c s="19" t="inlineStr" r="Q132">
         <is>
-          <t xml:space="preserve">external_tables</t>
+          <t xml:space="preserve">filegroups</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R132">
@@ -6661,7 +6702,7 @@
       <c s="13" t="str" r="P133"/>
       <c s="19" t="inlineStr" r="Q133">
         <is>
-          <t xml:space="preserve">filegroups</t>
+          <t xml:space="preserve">filetable_system_defined_objects</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R133">
@@ -6704,7 +6745,7 @@
       <c s="13" t="str" r="P134"/>
       <c s="19" t="inlineStr" r="Q134">
         <is>
-          <t xml:space="preserve">filetable_system_defined_objects</t>
+          <t xml:space="preserve">filetables</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R134">
@@ -6747,7 +6788,7 @@
       <c s="13" t="str" r="P135"/>
       <c s="19" t="inlineStr" r="Q135">
         <is>
-          <t xml:space="preserve">filetables</t>
+          <t xml:space="preserve">foreign_key_columns</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R135">
@@ -6790,7 +6831,7 @@
       <c s="13" t="str" r="P136"/>
       <c s="19" t="inlineStr" r="Q136">
         <is>
-          <t xml:space="preserve">foreign_key_columns</t>
+          <t xml:space="preserve">foreign_keys</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R136">
@@ -6802,7 +6843,7 @@
       <c s="12" t="str" r="T136"/>
       <c s="13" t="str" r="U136"/>
     </row>
-    <row r="137" ht="17" customHeight="0">
+    <row r="137" ht="17.05" customHeight="0">
       <c s="27" t="str" r="B137"/>
       <c s="28" t="str" r="D137"/>
       <c s="29" t="str" r="E137"/>
@@ -6833,7 +6874,7 @@
       <c s="13" t="str" r="P137"/>
       <c s="19" t="inlineStr" r="Q137">
         <is>
-          <t xml:space="preserve">foreign_keys</t>
+          <t xml:space="preserve">fulltext_catalogs</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R137">
@@ -6845,7 +6886,7 @@
       <c s="12" t="str" r="T137"/>
       <c s="13" t="str" r="U137"/>
     </row>
-    <row r="138" ht="17.05" customHeight="0">
+    <row r="138" ht="17" customHeight="0">
       <c s="27" t="str" r="B138"/>
       <c s="28" t="str" r="D138"/>
       <c s="29" t="str" r="E138"/>
@@ -6876,7 +6917,7 @@
       <c s="13" t="str" r="P138"/>
       <c s="19" t="inlineStr" r="Q138">
         <is>
-          <t xml:space="preserve">fulltext_catalogs</t>
+          <t xml:space="preserve">fulltext_index_catalog_usages</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R138">
@@ -6919,7 +6960,7 @@
       <c s="13" t="str" r="P139"/>
       <c s="19" t="inlineStr" r="Q139">
         <is>
-          <t xml:space="preserve">fulltext_index_catalog_usages</t>
+          <t xml:space="preserve">fulltext_index_columns</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R139">
@@ -6962,7 +7003,7 @@
       <c s="13" t="str" r="P140"/>
       <c s="19" t="inlineStr" r="Q140">
         <is>
-          <t xml:space="preserve">fulltext_index_columns</t>
+          <t xml:space="preserve">fulltext_index_fragments</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R140">
@@ -7005,7 +7046,7 @@
       <c s="13" t="str" r="P141"/>
       <c s="19" t="inlineStr" r="Q141">
         <is>
-          <t xml:space="preserve">fulltext_index_fragments</t>
+          <t xml:space="preserve">fulltext_indexes</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R141">
@@ -7048,7 +7089,7 @@
       <c s="13" t="str" r="P142"/>
       <c s="19" t="inlineStr" r="Q142">
         <is>
-          <t xml:space="preserve">fulltext_indexes</t>
+          <t xml:space="preserve">fulltext_stoplists</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R142">
@@ -7060,7 +7101,7 @@
       <c s="12" t="str" r="T142"/>
       <c s="13" t="str" r="U142"/>
     </row>
-    <row r="143" ht="17" customHeight="0">
+    <row r="143" ht="17.05" customHeight="0">
       <c s="27" t="str" r="B143"/>
       <c s="28" t="str" r="D143"/>
       <c s="29" t="str" r="E143"/>
@@ -7091,7 +7132,7 @@
       <c s="13" t="str" r="P143"/>
       <c s="19" t="inlineStr" r="Q143">
         <is>
-          <t xml:space="preserve">fulltext_stoplists</t>
+          <t xml:space="preserve">fulltext_stopwords</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R143">
@@ -7103,7 +7144,7 @@
       <c s="12" t="str" r="T143"/>
       <c s="13" t="str" r="U143"/>
     </row>
-    <row r="144" ht="17.05" customHeight="0">
+    <row r="144" ht="17" customHeight="0">
       <c s="27" t="str" r="B144"/>
       <c s="28" t="str" r="D144"/>
       <c s="29" t="str" r="E144"/>
@@ -7134,7 +7175,7 @@
       <c s="13" t="str" r="P144"/>
       <c s="19" t="inlineStr" r="Q144">
         <is>
-          <t xml:space="preserve">fulltext_stopwords</t>
+          <t xml:space="preserve">function_order_columns</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R144">
@@ -7177,7 +7218,7 @@
       <c s="13" t="str" r="P145"/>
       <c s="19" t="inlineStr" r="Q145">
         <is>
-          <t xml:space="preserve">function_order_columns</t>
+          <t xml:space="preserve">hash_indexes</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R145">
@@ -7220,7 +7261,7 @@
       <c s="13" t="str" r="P146"/>
       <c s="19" t="inlineStr" r="Q146">
         <is>
-          <t xml:space="preserve">hash_indexes</t>
+          <t xml:space="preserve">identity_columns</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R146">
@@ -7263,7 +7304,7 @@
       <c s="13" t="str" r="P147"/>
       <c s="19" t="inlineStr" r="Q147">
         <is>
-          <t xml:space="preserve">identity_columns</t>
+          <t xml:space="preserve">index_columns</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R147">
@@ -7306,7 +7347,7 @@
       <c s="13" t="str" r="P148"/>
       <c s="19" t="inlineStr" r="Q148">
         <is>
-          <t xml:space="preserve">index_columns</t>
+          <t xml:space="preserve">index_resumable_operations</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R148">
@@ -7349,7 +7390,7 @@
       <c s="13" t="str" r="P149"/>
       <c s="19" t="inlineStr" r="Q149">
         <is>
-          <t xml:space="preserve">index_resumable_operations</t>
+          <t xml:space="preserve">indexes</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R149">
@@ -7361,7 +7402,7 @@
       <c s="12" t="str" r="T149"/>
       <c s="13" t="str" r="U149"/>
     </row>
-    <row r="150" ht="17" customHeight="0">
+    <row r="150" ht="17.05" customHeight="0">
       <c s="27" t="str" r="B150"/>
       <c s="28" t="str" r="D150"/>
       <c s="29" t="str" r="E150"/>
@@ -7392,7 +7433,7 @@
       <c s="13" t="str" r="P150"/>
       <c s="19" t="inlineStr" r="Q150">
         <is>
-          <t xml:space="preserve">indexes</t>
+          <t xml:space="preserve">internal_partitions</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R150">
@@ -7404,7 +7445,7 @@
       <c s="12" t="str" r="T150"/>
       <c s="13" t="str" r="U150"/>
     </row>
-    <row r="151" ht="17.05" customHeight="0">
+    <row r="151" ht="17" customHeight="0">
       <c s="27" t="str" r="B151"/>
       <c s="28" t="str" r="D151"/>
       <c s="29" t="str" r="E151"/>
@@ -7435,7 +7476,7 @@
       <c s="13" t="str" r="P151"/>
       <c s="19" t="inlineStr" r="Q151">
         <is>
-          <t xml:space="preserve">internal_partitions</t>
+          <t xml:space="preserve">internal_tables</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R151">
@@ -7478,7 +7519,7 @@
       <c s="13" t="str" r="P152"/>
       <c s="19" t="inlineStr" r="Q152">
         <is>
-          <t xml:space="preserve">internal_tables</t>
+          <t xml:space="preserve">key_constraints</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R152">
@@ -7521,7 +7562,7 @@
       <c s="13" t="str" r="P153"/>
       <c s="19" t="inlineStr" r="Q153">
         <is>
-          <t xml:space="preserve">key_constraints</t>
+          <t xml:space="preserve">key_encryptions</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R153">
@@ -7564,7 +7605,7 @@
       <c s="13" t="str" r="P154"/>
       <c s="19" t="inlineStr" r="Q154">
         <is>
-          <t xml:space="preserve">key_encryptions</t>
+          <t xml:space="preserve">ledger_column_history</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R154">
@@ -7607,7 +7648,7 @@
       <c s="13" t="str" r="P155"/>
       <c s="19" t="inlineStr" r="Q155">
         <is>
-          <t xml:space="preserve">ledger_column_history</t>
+          <t xml:space="preserve">ledger_table_history</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R155">
@@ -7619,7 +7660,7 @@
       <c s="12" t="str" r="T155"/>
       <c s="13" t="str" r="U155"/>
     </row>
-    <row r="156" ht="17" customHeight="0">
+    <row r="156" ht="17.05" customHeight="0">
       <c s="27" t="str" r="B156"/>
       <c s="28" t="str" r="D156"/>
       <c s="29" t="str" r="E156"/>
@@ -7650,7 +7691,7 @@
       <c s="13" t="str" r="P156"/>
       <c s="19" t="inlineStr" r="Q156">
         <is>
-          <t xml:space="preserve">ledger_table_history</t>
+          <t xml:space="preserve">masked_columns</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R156">
@@ -7662,7 +7703,7 @@
       <c s="12" t="str" r="T156"/>
       <c s="13" t="str" r="U156"/>
     </row>
-    <row r="157" ht="17.05" customHeight="0">
+    <row r="157" ht="17" customHeight="0">
       <c s="27" t="str" r="B157"/>
       <c s="28" t="str" r="D157"/>
       <c s="29" t="str" r="E157"/>
@@ -7693,7 +7734,7 @@
       <c s="13" t="str" r="P157"/>
       <c s="19" t="inlineStr" r="Q157">
         <is>
-          <t xml:space="preserve">masked_columns</t>
+          <t xml:space="preserve">memory_optimized_tables_internal_attributes</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R157">
@@ -7736,7 +7777,7 @@
       <c s="13" t="str" r="P158"/>
       <c s="19" t="inlineStr" r="Q158">
         <is>
-          <t xml:space="preserve">memory_optimized_tables_internal_attributes</t>
+          <t xml:space="preserve">message_type_xml_schema_collection_usages</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R158">
@@ -7779,7 +7820,7 @@
       <c s="13" t="str" r="P159"/>
       <c s="19" t="inlineStr" r="Q159">
         <is>
-          <t xml:space="preserve">message_type_xml_schema_collection_usages</t>
+          <t xml:space="preserve">module_assembly_usages</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R159">
@@ -7822,7 +7863,7 @@
       <c s="13" t="str" r="P160"/>
       <c s="19" t="inlineStr" r="Q160">
         <is>
-          <t xml:space="preserve">module_assembly_usages</t>
+          <t xml:space="preserve">numbered_procedure_parameters</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R160">
@@ -7865,7 +7906,7 @@
       <c s="13" t="str" r="P161"/>
       <c s="19" t="inlineStr" r="Q161">
         <is>
-          <t xml:space="preserve">numbered_procedure_parameters</t>
+          <t xml:space="preserve">numbered_procedures</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R161">
@@ -7877,7 +7918,7 @@
       <c s="12" t="str" r="T161"/>
       <c s="13" t="str" r="U161"/>
     </row>
-    <row r="162" ht="17" customHeight="0">
+    <row r="162" ht="17.05" customHeight="0">
       <c s="27" t="str" r="B162"/>
       <c s="28" t="str" r="D162"/>
       <c s="29" t="str" r="E162"/>
@@ -7908,7 +7949,7 @@
       <c s="13" t="str" r="P162"/>
       <c s="19" t="inlineStr" r="Q162">
         <is>
-          <t xml:space="preserve">numbered_procedures</t>
+          <t xml:space="preserve">objects</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R162">
@@ -7920,7 +7961,7 @@
       <c s="12" t="str" r="T162"/>
       <c s="13" t="str" r="U162"/>
     </row>
-    <row r="163" ht="17.05" customHeight="0">
+    <row r="163" ht="17" customHeight="0">
       <c s="27" t="str" r="B163"/>
       <c s="28" t="str" r="D163"/>
       <c s="29" t="str" r="E163"/>
@@ -7951,7 +7992,7 @@
       <c s="13" t="str" r="P163"/>
       <c s="19" t="inlineStr" r="Q163">
         <is>
-          <t xml:space="preserve">objects</t>
+          <t xml:space="preserve">parameter_type_usages</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R163">
@@ -7994,7 +8035,7 @@
       <c s="13" t="str" r="P164"/>
       <c s="19" t="inlineStr" r="Q164">
         <is>
-          <t xml:space="preserve">parameter_type_usages</t>
+          <t xml:space="preserve">parameter_xml_schema_collection_usages</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R164">
@@ -8037,7 +8078,7 @@
       <c s="13" t="str" r="P165"/>
       <c s="19" t="inlineStr" r="Q165">
         <is>
-          <t xml:space="preserve">parameter_xml_schema_collection_usages</t>
+          <t xml:space="preserve">parameters</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R165">
@@ -8080,7 +8121,7 @@
       <c s="13" t="str" r="P166"/>
       <c s="19" t="inlineStr" r="Q166">
         <is>
-          <t xml:space="preserve">parameters</t>
+          <t xml:space="preserve">partition_functions</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R166">
@@ -8123,7 +8164,7 @@
       <c s="13" t="str" r="P167"/>
       <c s="19" t="inlineStr" r="Q167">
         <is>
-          <t xml:space="preserve">partition_functions</t>
+          <t xml:space="preserve">partition_parameters</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R167">
@@ -8166,7 +8207,7 @@
       <c s="13" t="str" r="P168"/>
       <c s="19" t="inlineStr" r="Q168">
         <is>
-          <t xml:space="preserve">partition_parameters</t>
+          <t xml:space="preserve">partition_range_values</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R168">
@@ -8178,7 +8219,7 @@
       <c s="12" t="str" r="T168"/>
       <c s="13" t="str" r="U168"/>
     </row>
-    <row r="169" ht="17" customHeight="0">
+    <row r="169" ht="17.05" customHeight="0">
       <c s="27" t="str" r="B169"/>
       <c s="28" t="str" r="D169"/>
       <c s="29" t="str" r="E169"/>
@@ -8209,7 +8250,7 @@
       <c s="13" t="str" r="P169"/>
       <c s="19" t="inlineStr" r="Q169">
         <is>
-          <t xml:space="preserve">partition_range_values</t>
+          <t xml:space="preserve">partition_schemes</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R169">
@@ -8221,7 +8262,7 @@
       <c s="12" t="str" r="T169"/>
       <c s="13" t="str" r="U169"/>
     </row>
-    <row r="170" ht="17.05" customHeight="0">
+    <row r="170" ht="17" customHeight="0">
       <c s="27" t="str" r="B170"/>
       <c s="28" t="str" r="D170"/>
       <c s="29" t="str" r="E170"/>
@@ -8252,7 +8293,7 @@
       <c s="13" t="str" r="P170"/>
       <c s="19" t="inlineStr" r="Q170">
         <is>
-          <t xml:space="preserve">partition_schemes</t>
+          <t xml:space="preserve">partitions</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R170">
@@ -8295,7 +8336,7 @@
       <c s="13" t="str" r="P171"/>
       <c s="19" t="inlineStr" r="Q171">
         <is>
-          <t xml:space="preserve">partitions</t>
+          <t xml:space="preserve">periods</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R171">
@@ -8338,7 +8379,7 @@
       <c s="13" t="str" r="P172"/>
       <c s="19" t="inlineStr" r="Q172">
         <is>
-          <t xml:space="preserve">periods</t>
+          <t xml:space="preserve">plan_guides</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R172">
@@ -8381,7 +8422,7 @@
       <c s="13" t="str" r="P173"/>
       <c s="19" t="inlineStr" r="Q173">
         <is>
-          <t xml:space="preserve">plan_guides</t>
+          <t xml:space="preserve">procedures</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R173">
@@ -8424,7 +8465,7 @@
       <c s="13" t="str" r="P174"/>
       <c s="19" t="inlineStr" r="Q174">
         <is>
-          <t xml:space="preserve">procedures</t>
+          <t xml:space="preserve">query_context_settings</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R174">
@@ -8436,7 +8477,7 @@
       <c s="12" t="str" r="T174"/>
       <c s="13" t="str" r="U174"/>
     </row>
-    <row r="175" ht="17" customHeight="0">
+    <row r="175" ht="17.05" customHeight="0">
       <c s="27" t="str" r="B175"/>
       <c s="28" t="str" r="D175"/>
       <c s="29" t="str" r="E175"/>
@@ -8467,7 +8508,7 @@
       <c s="13" t="str" r="P175"/>
       <c s="19" t="inlineStr" r="Q175">
         <is>
-          <t xml:space="preserve">query_context_settings</t>
+          <t xml:space="preserve">query_store_plan</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R175">
@@ -8479,7 +8520,7 @@
       <c s="12" t="str" r="T175"/>
       <c s="13" t="str" r="U175"/>
     </row>
-    <row r="176" ht="17.05" customHeight="0">
+    <row r="176" ht="17" customHeight="0">
       <c s="27" t="str" r="B176"/>
       <c s="28" t="str" r="D176"/>
       <c s="29" t="str" r="E176"/>
@@ -8510,7 +8551,7 @@
       <c s="13" t="str" r="P176"/>
       <c s="19" t="inlineStr" r="Q176">
         <is>
-          <t xml:space="preserve">query_store_plan</t>
+          <t xml:space="preserve">query_store_plan_feedback</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R176">
@@ -8553,7 +8594,7 @@
       <c s="13" t="str" r="P177"/>
       <c s="19" t="inlineStr" r="Q177">
         <is>
-          <t xml:space="preserve">query_store_plan_feedback</t>
+          <t xml:space="preserve">query_store_plan_forcing_locations</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R177">
@@ -8596,7 +8637,7 @@
       <c s="13" t="str" r="P178"/>
       <c s="19" t="inlineStr" r="Q178">
         <is>
-          <t xml:space="preserve">query_store_plan_forcing_locations</t>
+          <t xml:space="preserve">query_store_query</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R178">
@@ -8639,7 +8680,7 @@
       <c s="13" t="str" r="P179"/>
       <c s="19" t="inlineStr" r="Q179">
         <is>
-          <t xml:space="preserve">query_store_query</t>
+          <t xml:space="preserve">query_store_query_hints</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R179">
@@ -8682,7 +8723,7 @@
       <c s="13" t="str" r="P180"/>
       <c s="19" t="inlineStr" r="Q180">
         <is>
-          <t xml:space="preserve">query_store_query_hints</t>
+          <t xml:space="preserve">query_store_query_text</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R180">
@@ -8694,7 +8735,7 @@
       <c s="12" t="str" r="T180"/>
       <c s="13" t="str" r="U180"/>
     </row>
-    <row r="181" ht="17" customHeight="0">
+    <row r="181" ht="17.05" customHeight="0">
       <c s="27" t="str" r="B181"/>
       <c s="28" t="str" r="D181"/>
       <c s="29" t="str" r="E181"/>
@@ -8725,7 +8766,7 @@
       <c s="13" t="str" r="P181"/>
       <c s="19" t="inlineStr" r="Q181">
         <is>
-          <t xml:space="preserve">query_store_query_text</t>
+          <t xml:space="preserve">query_store_query_variant</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R181">
@@ -8737,7 +8778,7 @@
       <c s="12" t="str" r="T181"/>
       <c s="13" t="str" r="U181"/>
     </row>
-    <row r="182" ht="17.05" customHeight="0">
+    <row r="182" ht="17" customHeight="0">
       <c s="27" t="str" r="B182"/>
       <c s="28" t="str" r="D182"/>
       <c s="29" t="str" r="E182"/>
@@ -8768,7 +8809,7 @@
       <c s="13" t="str" r="P182"/>
       <c s="19" t="inlineStr" r="Q182">
         <is>
-          <t xml:space="preserve">query_store_query_variant</t>
+          <t xml:space="preserve">query_store_replicas</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R182">
@@ -8811,7 +8852,7 @@
       <c s="13" t="str" r="P183"/>
       <c s="19" t="inlineStr" r="Q183">
         <is>
-          <t xml:space="preserve">query_store_replicas</t>
+          <t xml:space="preserve">query_store_runtime_stats</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R183">
@@ -8854,7 +8895,7 @@
       <c s="13" t="str" r="P184"/>
       <c s="19" t="inlineStr" r="Q184">
         <is>
-          <t xml:space="preserve">query_store_runtime_stats</t>
+          <t xml:space="preserve">query_store_runtime_stats_interval</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R184">
@@ -8897,7 +8938,7 @@
       <c s="13" t="str" r="P185"/>
       <c s="19" t="inlineStr" r="Q185">
         <is>
-          <t xml:space="preserve">query_store_runtime_stats_interval</t>
+          <t xml:space="preserve">query_store_wait_stats</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R185">
@@ -8940,7 +8981,7 @@
       <c s="13" t="str" r="P186"/>
       <c s="19" t="inlineStr" r="Q186">
         <is>
-          <t xml:space="preserve">query_store_wait_stats</t>
+          <t xml:space="preserve">registered_search_properties</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R186">
@@ -8983,7 +9024,7 @@
       <c s="13" t="str" r="P187"/>
       <c s="19" t="inlineStr" r="Q187">
         <is>
-          <t xml:space="preserve">registered_search_properties</t>
+          <t xml:space="preserve">registered_search_property_lists</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R187">
@@ -8995,7 +9036,7 @@
       <c s="12" t="str" r="T187"/>
       <c s="13" t="str" r="U187"/>
     </row>
-    <row r="188" ht="17" customHeight="0">
+    <row r="188" ht="17.05" customHeight="0">
       <c s="27" t="str" r="B188"/>
       <c s="28" t="str" r="D188"/>
       <c s="29" t="str" r="E188"/>
@@ -9026,7 +9067,7 @@
       <c s="13" t="str" r="P188"/>
       <c s="19" t="inlineStr" r="Q188">
         <is>
-          <t xml:space="preserve">registered_search_property_lists</t>
+          <t xml:space="preserve">remote_data_archive_databases</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R188">
@@ -9038,7 +9079,7 @@
       <c s="12" t="str" r="T188"/>
       <c s="13" t="str" r="U188"/>
     </row>
-    <row r="189" ht="17.05" customHeight="0">
+    <row r="189" ht="17" customHeight="0">
       <c s="27" t="str" r="B189"/>
       <c s="28" t="str" r="D189"/>
       <c s="29" t="str" r="E189"/>
@@ -9069,7 +9110,7 @@
       <c s="13" t="str" r="P189"/>
       <c s="19" t="inlineStr" r="Q189">
         <is>
-          <t xml:space="preserve">remote_data_archive_databases</t>
+          <t xml:space="preserve">remote_data_archive_tables</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R189">
@@ -9112,7 +9153,7 @@
       <c s="13" t="str" r="P190"/>
       <c s="19" t="inlineStr" r="Q190">
         <is>
-          <t xml:space="preserve">remote_data_archive_tables</t>
+          <t xml:space="preserve">remote_service_bindings</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R190">
@@ -9155,7 +9196,7 @@
       <c s="13" t="str" r="P191"/>
       <c s="19" t="inlineStr" r="Q191">
         <is>
-          <t xml:space="preserve">remote_service_bindings</t>
+          <t xml:space="preserve">routes</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R191">
@@ -9198,7 +9239,7 @@
       <c s="13" t="str" r="P192"/>
       <c s="19" t="inlineStr" r="Q192">
         <is>
-          <t xml:space="preserve">routes</t>
+          <t xml:space="preserve">schemas</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R192">
@@ -9241,7 +9282,7 @@
       <c s="13" t="str" r="P193"/>
       <c s="19" t="inlineStr" r="Q193">
         <is>
-          <t xml:space="preserve">schemas</t>
+          <t xml:space="preserve">security_policies</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R193">
@@ -9253,7 +9294,7 @@
       <c s="12" t="str" r="T193"/>
       <c s="13" t="str" r="U193"/>
     </row>
-    <row r="194" ht="17" customHeight="0">
+    <row r="194" ht="17.05" customHeight="0">
       <c s="27" t="str" r="B194"/>
       <c s="28" t="str" r="D194"/>
       <c s="29" t="str" r="E194"/>
@@ -9284,7 +9325,7 @@
       <c s="13" t="str" r="P194"/>
       <c s="19" t="inlineStr" r="Q194">
         <is>
-          <t xml:space="preserve">security_policies</t>
+          <t xml:space="preserve">security_predicates</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R194">
@@ -9296,7 +9337,7 @@
       <c s="12" t="str" r="T194"/>
       <c s="13" t="str" r="U194"/>
     </row>
-    <row r="195" ht="17.05" customHeight="0">
+    <row r="195" ht="17" customHeight="0">
       <c s="27" t="str" r="B195"/>
       <c s="28" t="str" r="D195"/>
       <c s="29" t="str" r="E195"/>
@@ -9327,7 +9368,7 @@
       <c s="13" t="str" r="P195"/>
       <c s="19" t="inlineStr" r="Q195">
         <is>
-          <t xml:space="preserve">security_predicates</t>
+          <t xml:space="preserve">selective_xml_index_namespaces</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R195">
@@ -9370,7 +9411,7 @@
       <c s="13" t="str" r="P196"/>
       <c s="19" t="inlineStr" r="Q196">
         <is>
-          <t xml:space="preserve">selective_xml_index_namespaces</t>
+          <t xml:space="preserve">selective_xml_index_paths</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R196">
@@ -9413,7 +9454,7 @@
       <c s="13" t="str" r="P197"/>
       <c s="19" t="inlineStr" r="Q197">
         <is>
-          <t xml:space="preserve">selective_xml_index_paths</t>
+          <t xml:space="preserve">sensitivity_classifications</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R197">
@@ -9456,7 +9497,7 @@
       <c s="13" t="str" r="P198"/>
       <c s="19" t="inlineStr" r="Q198">
         <is>
-          <t xml:space="preserve">sensitivity_classifications</t>
+          <t xml:space="preserve">sequences</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R198">
@@ -9499,7 +9540,7 @@
       <c s="13" t="str" r="P199"/>
       <c s="19" t="inlineStr" r="Q199">
         <is>
-          <t xml:space="preserve">sequences</t>
+          <t xml:space="preserve">service_contract_message_usages</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R199">
@@ -9511,7 +9552,7 @@
       <c s="12" t="str" r="T199"/>
       <c s="13" t="str" r="U199"/>
     </row>
-    <row r="200" ht="17" customHeight="0">
+    <row r="200" ht="17.05" customHeight="0">
       <c s="27" t="str" r="B200"/>
       <c s="28" t="str" r="D200"/>
       <c s="29" t="str" r="E200"/>
@@ -9542,7 +9583,7 @@
       <c s="13" t="str" r="P200"/>
       <c s="19" t="inlineStr" r="Q200">
         <is>
-          <t xml:space="preserve">service_contract_message_usages</t>
+          <t xml:space="preserve">service_contract_usages</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R200">
@@ -9554,7 +9595,7 @@
       <c s="12" t="str" r="T200"/>
       <c s="13" t="str" r="U200"/>
     </row>
-    <row r="201" ht="17.05" customHeight="0">
+    <row r="201" ht="17" customHeight="0">
       <c s="27" t="str" r="B201"/>
       <c s="28" t="str" r="D201"/>
       <c s="29" t="str" r="E201"/>
@@ -9585,7 +9626,7 @@
       <c s="13" t="str" r="P201"/>
       <c s="19" t="inlineStr" r="Q201">
         <is>
-          <t xml:space="preserve">service_contract_usages</t>
+          <t xml:space="preserve">service_contracts</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R201">
@@ -9628,7 +9669,7 @@
       <c s="13" t="str" r="P202"/>
       <c s="19" t="inlineStr" r="Q202">
         <is>
-          <t xml:space="preserve">service_contracts</t>
+          <t xml:space="preserve">service_message_types</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R202">
@@ -9671,7 +9712,7 @@
       <c s="13" t="str" r="P203"/>
       <c s="19" t="inlineStr" r="Q203">
         <is>
-          <t xml:space="preserve">service_message_types</t>
+          <t xml:space="preserve">service_queue_usages</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R203">
@@ -9714,7 +9755,7 @@
       <c s="13" t="str" r="P204"/>
       <c s="19" t="inlineStr" r="Q204">
         <is>
-          <t xml:space="preserve">service_queue_usages</t>
+          <t xml:space="preserve">service_queues</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R204">
@@ -9757,7 +9798,7 @@
       <c s="13" t="str" r="P205"/>
       <c s="19" t="inlineStr" r="Q205">
         <is>
-          <t xml:space="preserve">service_queues</t>
+          <t xml:space="preserve">services</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R205">
@@ -9800,7 +9841,7 @@
       <c s="13" t="str" r="P206"/>
       <c s="19" t="inlineStr" r="Q206">
         <is>
-          <t xml:space="preserve">services</t>
+          <t xml:space="preserve">spatial_index_tessellations</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R206">
@@ -9812,7 +9853,7 @@
       <c s="12" t="str" r="T206"/>
       <c s="13" t="str" r="U206"/>
     </row>
-    <row r="207" ht="17" customHeight="0">
+    <row r="207" ht="17.05" customHeight="0">
       <c s="27" t="str" r="B207"/>
       <c s="28" t="str" r="D207"/>
       <c s="29" t="str" r="E207"/>
@@ -9843,7 +9884,7 @@
       <c s="13" t="str" r="P207"/>
       <c s="19" t="inlineStr" r="Q207">
         <is>
-          <t xml:space="preserve">spatial_index_tessellations</t>
+          <t xml:space="preserve">spatial_indexes</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R207">
@@ -9855,7 +9896,7 @@
       <c s="12" t="str" r="T207"/>
       <c s="13" t="str" r="U207"/>
     </row>
-    <row r="208" ht="17.05" customHeight="0">
+    <row r="208" ht="17" customHeight="0">
       <c s="27" t="str" r="B208"/>
       <c s="28" t="str" r="D208"/>
       <c s="29" t="str" r="E208"/>
@@ -9886,7 +9927,7 @@
       <c s="13" t="str" r="P208"/>
       <c s="19" t="inlineStr" r="Q208">
         <is>
-          <t xml:space="preserve">spatial_indexes</t>
+          <t xml:space="preserve">sql_dependencies</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R208">
@@ -9929,7 +9970,7 @@
       <c s="13" t="str" r="P209"/>
       <c s="19" t="inlineStr" r="Q209">
         <is>
-          <t xml:space="preserve">sql_dependencies</t>
+          <t xml:space="preserve">sql_modules</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R209">
@@ -9972,7 +10013,7 @@
       <c s="13" t="str" r="P210"/>
       <c s="19" t="inlineStr" r="Q210">
         <is>
-          <t xml:space="preserve">sql_modules</t>
+          <t xml:space="preserve">stats</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R210">
@@ -10015,7 +10056,7 @@
       <c s="13" t="str" r="P211"/>
       <c s="19" t="inlineStr" r="Q211">
         <is>
-          <t xml:space="preserve">stats</t>
+          <t xml:space="preserve">stats_columns</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R211">
@@ -10058,7 +10099,7 @@
       <c s="13" t="str" r="P212"/>
       <c s="19" t="inlineStr" r="Q212">
         <is>
-          <t xml:space="preserve">stats_columns</t>
+          <t xml:space="preserve">symmetric_keys</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R212">
@@ -10070,7 +10111,7 @@
       <c s="12" t="str" r="T212"/>
       <c s="13" t="str" r="U212"/>
     </row>
-    <row r="213" ht="17" customHeight="0">
+    <row r="213" ht="17.05" customHeight="0">
       <c s="27" t="str" r="B213"/>
       <c s="28" t="str" r="D213"/>
       <c s="29" t="str" r="E213"/>
@@ -10101,7 +10142,7 @@
       <c s="13" t="str" r="P213"/>
       <c s="19" t="inlineStr" r="Q213">
         <is>
-          <t xml:space="preserve">symmetric_keys</t>
+          <t xml:space="preserve">synonyms</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R213">
@@ -10113,7 +10154,7 @@
       <c s="12" t="str" r="T213"/>
       <c s="13" t="str" r="U213"/>
     </row>
-    <row r="214" ht="17.05" customHeight="0">
+    <row r="214" ht="17" customHeight="0">
       <c s="27" t="str" r="B214"/>
       <c s="28" t="str" r="D214"/>
       <c s="29" t="str" r="E214"/>
@@ -10144,7 +10185,7 @@
       <c s="13" t="str" r="P214"/>
       <c s="19" t="inlineStr" r="Q214">
         <is>
-          <t xml:space="preserve">synonyms</t>
+          <t xml:space="preserve">syscolumns</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R214">
@@ -10187,7 +10228,7 @@
       <c s="13" t="str" r="P215"/>
       <c s="19" t="inlineStr" r="Q215">
         <is>
-          <t xml:space="preserve">syscolumns</t>
+          <t xml:space="preserve">syscomments</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R215">
@@ -10230,7 +10271,7 @@
       <c s="13" t="str" r="P216"/>
       <c s="19" t="inlineStr" r="Q216">
         <is>
-          <t xml:space="preserve">syscomments</t>
+          <t xml:space="preserve">sysconstraints</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R216">
@@ -10273,7 +10314,7 @@
       <c s="13" t="str" r="P217"/>
       <c s="19" t="inlineStr" r="Q217">
         <is>
-          <t xml:space="preserve">sysconstraints</t>
+          <t xml:space="preserve">sysdepends</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R217">
@@ -10316,7 +10357,7 @@
       <c s="13" t="str" r="P218"/>
       <c s="19" t="inlineStr" r="Q218">
         <is>
-          <t xml:space="preserve">sysdepends</t>
+          <t xml:space="preserve">sysfilegroups</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R218">
@@ -10359,7 +10400,7 @@
       <c s="13" t="str" r="P219"/>
       <c s="19" t="inlineStr" r="Q219">
         <is>
-          <t xml:space="preserve">sysfilegroups</t>
+          <t xml:space="preserve">sysfiles</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R219">
@@ -10371,7 +10412,7 @@
       <c s="12" t="str" r="T219"/>
       <c s="13" t="str" r="U219"/>
     </row>
-    <row r="220" ht="17" customHeight="0">
+    <row r="220" ht="17.05" customHeight="0">
       <c s="27" t="str" r="B220"/>
       <c s="28" t="str" r="D220"/>
       <c s="29" t="str" r="E220"/>
@@ -10402,7 +10443,7 @@
       <c s="13" t="str" r="P220"/>
       <c s="19" t="inlineStr" r="Q220">
         <is>
-          <t xml:space="preserve">sysfiles</t>
+          <t xml:space="preserve">sysforeignkeys</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R220">
@@ -10414,7 +10455,7 @@
       <c s="12" t="str" r="T220"/>
       <c s="13" t="str" r="U220"/>
     </row>
-    <row r="221" ht="17.05" customHeight="0">
+    <row r="221" ht="17" customHeight="0">
       <c s="27" t="str" r="B221"/>
       <c s="28" t="str" r="D221"/>
       <c s="29" t="str" r="E221"/>
@@ -10445,7 +10486,7 @@
       <c s="13" t="str" r="P221"/>
       <c s="19" t="inlineStr" r="Q221">
         <is>
-          <t xml:space="preserve">sysforeignkeys</t>
+          <t xml:space="preserve">sysfulltextcatalogs</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R221">
@@ -10488,7 +10529,7 @@
       <c s="13" t="str" r="P222"/>
       <c s="19" t="inlineStr" r="Q222">
         <is>
-          <t xml:space="preserve">sysfulltextcatalogs</t>
+          <t xml:space="preserve">sysindexes</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R222">
@@ -10531,7 +10572,7 @@
       <c s="13" t="str" r="P223"/>
       <c s="19" t="inlineStr" r="Q223">
         <is>
-          <t xml:space="preserve">sysindexes</t>
+          <t xml:space="preserve">sysindexkeys</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R223">
@@ -10574,7 +10615,7 @@
       <c s="13" t="str" r="P224"/>
       <c s="19" t="inlineStr" r="Q224">
         <is>
-          <t xml:space="preserve">sysindexkeys</t>
+          <t xml:space="preserve">sysmembers</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R224">
@@ -10617,7 +10658,7 @@
       <c s="13" t="str" r="P225"/>
       <c s="19" t="inlineStr" r="Q225">
         <is>
-          <t xml:space="preserve">sysmembers</t>
+          <t xml:space="preserve">sysobjects</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R225">
@@ -10629,7 +10670,7 @@
       <c s="12" t="str" r="T225"/>
       <c s="13" t="str" r="U225"/>
     </row>
-    <row r="226" ht="17" customHeight="0">
+    <row r="226" ht="17.05" customHeight="0">
       <c s="27" t="str" r="B226"/>
       <c s="28" t="str" r="D226"/>
       <c s="29" t="str" r="E226"/>
@@ -10660,7 +10701,7 @@
       <c s="13" t="str" r="P226"/>
       <c s="19" t="inlineStr" r="Q226">
         <is>
-          <t xml:space="preserve">sysobjects</t>
+          <t xml:space="preserve">syspermissions</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R226">
@@ -10672,7 +10713,7 @@
       <c s="12" t="str" r="T226"/>
       <c s="13" t="str" r="U226"/>
     </row>
-    <row r="227" ht="17.05" customHeight="0">
+    <row r="227" ht="17" customHeight="0">
       <c s="27" t="str" r="B227"/>
       <c s="28" t="str" r="D227"/>
       <c s="29" t="str" r="E227"/>
@@ -10703,7 +10744,7 @@
       <c s="13" t="str" r="P227"/>
       <c s="19" t="inlineStr" r="Q227">
         <is>
-          <t xml:space="preserve">syspermissions</t>
+          <t xml:space="preserve">sysprotects</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R227">
@@ -10746,7 +10787,7 @@
       <c s="13" t="str" r="P228"/>
       <c s="19" t="inlineStr" r="Q228">
         <is>
-          <t xml:space="preserve">sysprotects</t>
+          <t xml:space="preserve">sysreferences</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R228">
@@ -10789,7 +10830,7 @@
       <c s="13" t="str" r="P229"/>
       <c s="19" t="inlineStr" r="Q229">
         <is>
-          <t xml:space="preserve">sysreferences</t>
+          <t xml:space="preserve">system_columns</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R229">
@@ -10832,7 +10873,7 @@
       <c s="13" t="str" r="P230"/>
       <c s="19" t="inlineStr" r="Q230">
         <is>
-          <t xml:space="preserve">system_columns</t>
+          <t xml:space="preserve">system_objects</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R230">
@@ -10875,7 +10916,7 @@
       <c s="13" t="str" r="P231"/>
       <c s="19" t="inlineStr" r="Q231">
         <is>
-          <t xml:space="preserve">system_objects</t>
+          <t xml:space="preserve">system_parameters</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R231">
@@ -10887,7 +10928,7 @@
       <c s="12" t="str" r="T231"/>
       <c s="13" t="str" r="U231"/>
     </row>
-    <row r="232" ht="17" customHeight="0">
+    <row r="232" ht="17.05" customHeight="0">
       <c s="27" t="str" r="B232"/>
       <c s="28" t="str" r="D232"/>
       <c s="29" t="str" r="E232"/>
@@ -10918,7 +10959,7 @@
       <c s="13" t="str" r="P232"/>
       <c s="19" t="inlineStr" r="Q232">
         <is>
-          <t xml:space="preserve">system_parameters</t>
+          <t xml:space="preserve">system_sql_modules</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R232">
@@ -10930,7 +10971,7 @@
       <c s="12" t="str" r="T232"/>
       <c s="13" t="str" r="U232"/>
     </row>
-    <row r="233" ht="17.05" customHeight="0">
+    <row r="233" ht="17" customHeight="0">
       <c s="27" t="str" r="B233"/>
       <c s="28" t="str" r="D233"/>
       <c s="29" t="str" r="E233"/>
@@ -10961,7 +11002,7 @@
       <c s="13" t="str" r="P233"/>
       <c s="19" t="inlineStr" r="Q233">
         <is>
-          <t xml:space="preserve">system_sql_modules</t>
+          <t xml:space="preserve">system_views</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R233">
@@ -11004,7 +11045,7 @@
       <c s="13" t="str" r="P234"/>
       <c s="19" t="inlineStr" r="Q234">
         <is>
-          <t xml:space="preserve">system_views</t>
+          <t xml:space="preserve">systypes</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R234">
@@ -11047,7 +11088,7 @@
       <c s="13" t="str" r="P235"/>
       <c s="19" t="inlineStr" r="Q235">
         <is>
-          <t xml:space="preserve">systypes</t>
+          <t xml:space="preserve">sysusers</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R235">
@@ -11090,7 +11131,7 @@
       <c s="13" t="str" r="P236"/>
       <c s="19" t="inlineStr" r="Q236">
         <is>
-          <t xml:space="preserve">sysusers</t>
+          <t xml:space="preserve">table_types</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R236">
@@ -11133,7 +11174,7 @@
       <c s="13" t="str" r="P237"/>
       <c s="19" t="inlineStr" r="Q237">
         <is>
-          <t xml:space="preserve">table_types</t>
+          <t xml:space="preserve">tables</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R237">
@@ -11176,7 +11217,7 @@
       <c s="13" t="str" r="P238"/>
       <c s="19" t="inlineStr" r="Q238">
         <is>
-          <t xml:space="preserve">tables</t>
+          <t xml:space="preserve">time_zone_info</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R238">
@@ -11188,7 +11229,7 @@
       <c s="12" t="str" r="T238"/>
       <c s="13" t="str" r="U238"/>
     </row>
-    <row r="239" ht="17" customHeight="0">
+    <row r="239" ht="17.05" customHeight="0">
       <c s="27" t="str" r="B239"/>
       <c s="28" t="str" r="D239"/>
       <c s="29" t="str" r="E239"/>
@@ -11219,7 +11260,7 @@
       <c s="13" t="str" r="P239"/>
       <c s="19" t="inlineStr" r="Q239">
         <is>
-          <t xml:space="preserve">time_zone_info</t>
+          <t xml:space="preserve">transmission_queue</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R239">
@@ -11231,7 +11272,7 @@
       <c s="12" t="str" r="T239"/>
       <c s="13" t="str" r="U239"/>
     </row>
-    <row r="240" ht="17.05" customHeight="0">
+    <row r="240" ht="17" customHeight="0">
       <c s="27" t="str" r="B240"/>
       <c s="28" t="str" r="D240"/>
       <c s="29" t="str" r="E240"/>
@@ -11262,7 +11303,7 @@
       <c s="13" t="str" r="P240"/>
       <c s="19" t="inlineStr" r="Q240">
         <is>
-          <t xml:space="preserve">transmission_queue</t>
+          <t xml:space="preserve">trigger_events</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R240">
@@ -11305,7 +11346,7 @@
       <c s="13" t="str" r="P241"/>
       <c s="19" t="inlineStr" r="Q241">
         <is>
-          <t xml:space="preserve">trigger_events</t>
+          <t xml:space="preserve">triggers</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R241">
@@ -11348,7 +11389,7 @@
       <c s="13" t="str" r="P242"/>
       <c s="19" t="inlineStr" r="Q242">
         <is>
-          <t xml:space="preserve">triggers</t>
+          <t xml:space="preserve">type_assembly_usages</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R242">
@@ -11391,7 +11432,7 @@
       <c s="13" t="str" r="P243"/>
       <c s="19" t="inlineStr" r="Q243">
         <is>
-          <t xml:space="preserve">type_assembly_usages</t>
+          <t xml:space="preserve">types</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R243">
@@ -11434,7 +11475,7 @@
       <c s="13" t="str" r="P244"/>
       <c s="19" t="inlineStr" r="Q244">
         <is>
-          <t xml:space="preserve">types</t>
+          <t xml:space="preserve">views</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R244">
@@ -11446,7 +11487,7 @@
       <c s="12" t="str" r="T244"/>
       <c s="13" t="str" r="U244"/>
     </row>
-    <row r="245" ht="17" customHeight="0">
+    <row r="245" ht="17.05" customHeight="0">
       <c s="27" t="str" r="B245"/>
       <c s="28" t="str" r="D245"/>
       <c s="29" t="str" r="E245"/>
@@ -11477,7 +11518,7 @@
       <c s="13" t="str" r="P245"/>
       <c s="19" t="inlineStr" r="Q245">
         <is>
-          <t xml:space="preserve">views</t>
+          <t xml:space="preserve">xml_indexes</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R245">
@@ -11489,7 +11530,7 @@
       <c s="12" t="str" r="T245"/>
       <c s="13" t="str" r="U245"/>
     </row>
-    <row r="246" ht="17.05" customHeight="0">
+    <row r="246" ht="17" customHeight="0">
       <c s="27" t="str" r="B246"/>
       <c s="28" t="str" r="D246"/>
       <c s="29" t="str" r="E246"/>
@@ -11520,7 +11561,7 @@
       <c s="13" t="str" r="P246"/>
       <c s="19" t="inlineStr" r="Q246">
         <is>
-          <t xml:space="preserve">xml_indexes</t>
+          <t xml:space="preserve">xml_schema_attributes</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R246">
@@ -11563,7 +11604,7 @@
       <c s="13" t="str" r="P247"/>
       <c s="19" t="inlineStr" r="Q247">
         <is>
-          <t xml:space="preserve">xml_schema_attributes</t>
+          <t xml:space="preserve">xml_schema_collections</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R247">
@@ -11606,7 +11647,7 @@
       <c s="13" t="str" r="P248"/>
       <c s="19" t="inlineStr" r="Q248">
         <is>
-          <t xml:space="preserve">xml_schema_collections</t>
+          <t xml:space="preserve">xml_schema_component_placements</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R248">
@@ -11649,7 +11690,7 @@
       <c s="13" t="str" r="P249"/>
       <c s="19" t="inlineStr" r="Q249">
         <is>
-          <t xml:space="preserve">xml_schema_component_placements</t>
+          <t xml:space="preserve">xml_schema_components</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R249">
@@ -11692,7 +11733,7 @@
       <c s="13" t="str" r="P250"/>
       <c s="19" t="inlineStr" r="Q250">
         <is>
-          <t xml:space="preserve">xml_schema_components</t>
+          <t xml:space="preserve">xml_schema_elements</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R250">
@@ -11704,7 +11745,7 @@
       <c s="12" t="str" r="T250"/>
       <c s="13" t="str" r="U250"/>
     </row>
-    <row r="251" ht="17" customHeight="0">
+    <row r="251" ht="17.05" customHeight="0">
       <c s="27" t="str" r="B251"/>
       <c s="28" t="str" r="D251"/>
       <c s="29" t="str" r="E251"/>
@@ -11735,7 +11776,7 @@
       <c s="13" t="str" r="P251"/>
       <c s="19" t="inlineStr" r="Q251">
         <is>
-          <t xml:space="preserve">xml_schema_elements</t>
+          <t xml:space="preserve">xml_schema_facets</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R251">
@@ -11747,7 +11788,7 @@
       <c s="12" t="str" r="T251"/>
       <c s="13" t="str" r="U251"/>
     </row>
-    <row r="252" ht="17.05" customHeight="0">
+    <row r="252" ht="17" customHeight="0">
       <c s="27" t="str" r="B252"/>
       <c s="28" t="str" r="D252"/>
       <c s="29" t="str" r="E252"/>
@@ -11778,7 +11819,7 @@
       <c s="13" t="str" r="P252"/>
       <c s="19" t="inlineStr" r="Q252">
         <is>
-          <t xml:space="preserve">xml_schema_facets</t>
+          <t xml:space="preserve">xml_schema_model_groups</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R252">
@@ -11821,7 +11862,7 @@
       <c s="13" t="str" r="P253"/>
       <c s="19" t="inlineStr" r="Q253">
         <is>
-          <t xml:space="preserve">xml_schema_model_groups</t>
+          <t xml:space="preserve">xml_schema_namespaces</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R253">
@@ -11864,7 +11905,7 @@
       <c s="13" t="str" r="P254"/>
       <c s="19" t="inlineStr" r="Q254">
         <is>
-          <t xml:space="preserve">xml_schema_namespaces</t>
+          <t xml:space="preserve">xml_schema_types</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R254">
@@ -11907,7 +11948,7 @@
       <c s="13" t="str" r="P255"/>
       <c s="19" t="inlineStr" r="Q255">
         <is>
-          <t xml:space="preserve">xml_schema_types</t>
+          <t xml:space="preserve">xml_schema_wildcard_namespaces</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R255">
@@ -11920,11 +11961,14 @@
       <c s="13" t="str" r="U255"/>
     </row>
     <row r="256" ht="17" customHeight="0">
-      <c s="27" t="str" r="B256"/>
-      <c s="28" t="str" r="D256"/>
-      <c s="29" t="str" r="E256"/>
-      <c s="27" t="str" r="F256"/>
-      <c s="28" t="str" r="I256"/>
+      <c s="23" t="str" r="B256"/>
+      <c s="24" t="str" r="C256"/>
+      <c s="25" t="str" r="D256"/>
+      <c s="26" t="str" r="E256"/>
+      <c s="23" t="str" r="F256"/>
+      <c s="24" t="str" r="G256"/>
+      <c s="24" t="str" r="H256"/>
+      <c s="25" t="str" r="I256"/>
       <c s="19" t="inlineStr" r="J256">
         <is>
           <t xml:space="preserve">GRANT</t>
@@ -11950,7 +11994,7 @@
       <c s="13" t="str" r="P256"/>
       <c s="19" t="inlineStr" r="Q256">
         <is>
-          <t xml:space="preserve">xml_schema_wildcard_namespaces</t>
+          <t xml:space="preserve">xml_schema_wildcards</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R256">
@@ -11962,53 +12006,7 @@
       <c s="12" t="str" r="T256"/>
       <c s="13" t="str" r="U256"/>
     </row>
-    <row r="257" ht="17" customHeight="0">
-      <c s="23" t="str" r="B257"/>
-      <c s="24" t="str" r="C257"/>
-      <c s="25" t="str" r="D257"/>
-      <c s="26" t="str" r="E257"/>
-      <c s="23" t="str" r="F257"/>
-      <c s="24" t="str" r="G257"/>
-      <c s="24" t="str" r="H257"/>
-      <c s="25" t="str" r="I257"/>
-      <c s="19" t="inlineStr" r="J257">
-        <is>
-          <t xml:space="preserve">GRANT</t>
-        </is>
-      </c>
-      <c s="19" t="inlineStr" r="K257">
-        <is>
-          <t xml:space="preserve">SELECT</t>
-        </is>
-      </c>
-      <c s="19" t="inlineStr" r="L257">
-        <is>
-          <t xml:space="preserve">VIEW</t>
-        </is>
-      </c>
-      <c s="12" t="str" r="M257"/>
-      <c s="13" t="str" r="N257"/>
-      <c s="19" t="inlineStr" r="O257">
-        <is>
-          <t xml:space="preserve">sys</t>
-        </is>
-      </c>
-      <c s="13" t="str" r="P257"/>
-      <c s="19" t="inlineStr" r="Q257">
-        <is>
-          <t xml:space="preserve">xml_schema_wildcards</t>
-        </is>
-      </c>
-      <c s="20" t="inlineStr" r="R257">
-        <is>
-          <t xml:space="preserve">*</t>
-        </is>
-      </c>
-      <c s="12" t="str" r="S257"/>
-      <c s="12" t="str" r="T257"/>
-      <c s="13" t="str" r="U257"/>
-    </row>
-    <row r="258" ht="0.05" customHeight="1"/>
+    <row r="257" ht="0.05" customHeight="1"/>
   </sheetData>
   <mergeCells>
     <mergeCell ref="T1:T6"/>
@@ -12031,44 +12029,47 @@
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="H14:L14"/>
     <mergeCell ref="C16:V16"/>
-    <mergeCell ref="B19:U19"/>
+    <mergeCell ref="B18:U18"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="F20:I20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:P20"/>
+    <mergeCell ref="R20:U20"/>
     <mergeCell ref="B21:D21"/>
     <mergeCell ref="F21:I21"/>
     <mergeCell ref="L21:N21"/>
     <mergeCell ref="O21:P21"/>
     <mergeCell ref="R21:U21"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="F22:I22"/>
+    <mergeCell ref="B22:D23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="F22:I23"/>
     <mergeCell ref="L22:N22"/>
     <mergeCell ref="O22:P22"/>
     <mergeCell ref="R22:U22"/>
-    <mergeCell ref="B23:D24"/>
-    <mergeCell ref="E23:E24"/>
-    <mergeCell ref="F23:I24"/>
     <mergeCell ref="L23:N23"/>
     <mergeCell ref="O23:P23"/>
     <mergeCell ref="R23:U23"/>
+    <mergeCell ref="B24:D51"/>
+    <mergeCell ref="E24:E26"/>
+    <mergeCell ref="F24:I26"/>
     <mergeCell ref="L24:N24"/>
     <mergeCell ref="O24:P24"/>
     <mergeCell ref="R24:U24"/>
-    <mergeCell ref="B25:D52"/>
-    <mergeCell ref="E25:E27"/>
-    <mergeCell ref="F25:I27"/>
     <mergeCell ref="L25:N25"/>
     <mergeCell ref="O25:P25"/>
     <mergeCell ref="R25:U25"/>
     <mergeCell ref="L26:N26"/>
     <mergeCell ref="O26:P26"/>
     <mergeCell ref="R26:U26"/>
+    <mergeCell ref="F27:I27"/>
     <mergeCell ref="L27:N27"/>
     <mergeCell ref="O27:P27"/>
     <mergeCell ref="R27:U27"/>
-    <mergeCell ref="F28:I28"/>
+    <mergeCell ref="E28:E33"/>
+    <mergeCell ref="F28:I33"/>
     <mergeCell ref="L28:N28"/>
     <mergeCell ref="O28:P28"/>
     <mergeCell ref="R28:U28"/>
-    <mergeCell ref="E29:E34"/>
-    <mergeCell ref="F29:I34"/>
     <mergeCell ref="L29:N29"/>
     <mergeCell ref="O29:P29"/>
     <mergeCell ref="R29:U29"/>
@@ -12084,11 +12085,11 @@
     <mergeCell ref="L33:N33"/>
     <mergeCell ref="O33:P33"/>
     <mergeCell ref="R33:U33"/>
+    <mergeCell ref="E34:E47"/>
+    <mergeCell ref="F34:I47"/>
     <mergeCell ref="L34:N34"/>
     <mergeCell ref="O34:P34"/>
     <mergeCell ref="R34:U34"/>
-    <mergeCell ref="E35:E48"/>
-    <mergeCell ref="F35:I48"/>
     <mergeCell ref="L35:N35"/>
     <mergeCell ref="O35:P35"/>
     <mergeCell ref="R35:U35"/>
@@ -12128,11 +12129,11 @@
     <mergeCell ref="L47:N47"/>
     <mergeCell ref="O47:P47"/>
     <mergeCell ref="R47:U47"/>
+    <mergeCell ref="E48:E51"/>
+    <mergeCell ref="F48:I51"/>
     <mergeCell ref="L48:N48"/>
     <mergeCell ref="O48:P48"/>
     <mergeCell ref="R48:U48"/>
-    <mergeCell ref="E49:E52"/>
-    <mergeCell ref="F49:I52"/>
     <mergeCell ref="L49:N49"/>
     <mergeCell ref="O49:P49"/>
     <mergeCell ref="R49:U49"/>
@@ -12142,17 +12143,17 @@
     <mergeCell ref="L51:N51"/>
     <mergeCell ref="O51:P51"/>
     <mergeCell ref="R51:U51"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="F52:I52"/>
     <mergeCell ref="L52:N52"/>
     <mergeCell ref="O52:P52"/>
     <mergeCell ref="R52:U52"/>
-    <mergeCell ref="B53:D53"/>
-    <mergeCell ref="F53:I53"/>
+    <mergeCell ref="B53:D256"/>
+    <mergeCell ref="E53:E256"/>
+    <mergeCell ref="F53:I256"/>
     <mergeCell ref="L53:N53"/>
     <mergeCell ref="O53:P53"/>
     <mergeCell ref="R53:U53"/>
-    <mergeCell ref="B54:D257"/>
-    <mergeCell ref="E54:E257"/>
-    <mergeCell ref="F54:I257"/>
     <mergeCell ref="L54:N54"/>
     <mergeCell ref="O54:P54"/>
     <mergeCell ref="R54:U54"/>
@@ -12762,16 +12763,13 @@
     <mergeCell ref="L256:N256"/>
     <mergeCell ref="O256:P256"/>
     <mergeCell ref="R256:U256"/>
-    <mergeCell ref="L257:N257"/>
-    <mergeCell ref="O257:P257"/>
-    <mergeCell ref="R257:U257"/>
   </mergeCells>
   <pageMargins left="0" right="0" top="0" bottom="0.766566929133858" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
     <oddFooter>&amp;L&amp;"Arial,Regular"&amp;7 Bericht '/SQLSERVER_RechteAudit_V6' 
 &amp;"-,Regular"Berichtsverantwortlicher: Markus Hofmann (IB15MH) &amp;C&amp;"Arial,Regular"&amp;10  &amp;R&amp;"Arial,Regular"&amp;7 Generiert von LAN\\ps733 
-&amp;"-,Regular"19.06.2026 10:59:29 Uhr 
+&amp;"-,Regular"19.06.2026 11:01:25 Uhr 
 &amp;"-,Regular"Seite &amp;P von &amp;N </oddFooter>
   </headerFooter>
   <drawing r:id="rId14"/>
@@ -13034,10 +13032,9 @@
       <c s="9" t="str" r="U16"/>
       <c s="9" t="str" r="V16"/>
     </row>
-    <row r="17" ht="7" customHeight="1"/>
-    <row r="18" ht="5.65" customHeight="1"/>
-    <row r="19" ht="17" customHeight="1">
-      <c s="10" t="inlineStr" r="B19">
+    <row r="17" ht="5.65" customHeight="1"/>
+    <row r="18" ht="17" customHeight="1">
+      <c s="10" t="inlineStr" r="B18">
         <is>
           <t xml:space="preserve">Globale Berechtigungen.
 Die im Folgenden dargestellten Rechte wurden seit der letzten Rezertifizierung entzogen.
@@ -13045,67 +13042,67 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="5.65" customHeight="1"/>
+    <row r="19" ht="5.65" customHeight="1"/>
+    <row r="20" ht="17" customHeight="0">
+      <c s="14" t="inlineStr" r="B20">
+        <is>
+          <t xml:space="preserve">AD-Gruppe / AD-User / DB-User</t>
+        </is>
+      </c>
+      <c s="15" t="str" r="C20"/>
+      <c s="16" t="str" r="D20"/>
+      <c s="14" t="inlineStr" r="E20">
+        <is>
+          <t xml:space="preserve">DB-Rolle </t>
+        </is>
+      </c>
+      <c s="14" t="inlineStr" r="F20">
+        <is>
+          <t xml:space="preserve">Recht vergeben an</t>
+        </is>
+      </c>
+      <c s="15" t="str" r="G20"/>
+      <c s="15" t="str" r="H20"/>
+      <c s="16" t="str" r="I20"/>
+      <c s="14" t="inlineStr" r="J20">
+        <is>
+          <t xml:space="preserve">Zugriff</t>
+        </is>
+      </c>
+      <c s="14" t="inlineStr" r="K20">
+        <is>
+          <t xml:space="preserve">Berechtigung</t>
+        </is>
+      </c>
+      <c s="14" t="inlineStr" r="L20">
+        <is>
+          <t xml:space="preserve">Objekttyp</t>
+        </is>
+      </c>
+      <c s="15" t="str" r="M20"/>
+      <c s="16" t="str" r="N20"/>
+      <c s="14" t="inlineStr" r="O20">
+        <is>
+          <t xml:space="preserve">Schema</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P20"/>
+      <c s="14" t="inlineStr" r="Q20">
+        <is>
+          <t xml:space="preserve">Objektname</t>
+        </is>
+      </c>
+      <c s="14" t="inlineStr" r="R20">
+        <is>
+          <t xml:space="preserve">Spalte</t>
+        </is>
+      </c>
+      <c s="15" t="str" r="S20"/>
+      <c s="15" t="str" r="T20"/>
+      <c s="16" t="str" r="U20"/>
+    </row>
     <row r="21" ht="17" customHeight="0">
-      <c s="14" t="inlineStr" r="B21">
-        <is>
-          <t xml:space="preserve">AD-Gruppe / AD-User / DB-User</t>
-        </is>
-      </c>
-      <c s="15" t="str" r="C21"/>
-      <c s="16" t="str" r="D21"/>
-      <c s="14" t="inlineStr" r="E21">
-        <is>
-          <t xml:space="preserve">DB-Rolle </t>
-        </is>
-      </c>
-      <c s="14" t="inlineStr" r="F21">
-        <is>
-          <t xml:space="preserve">Recht vergeben an</t>
-        </is>
-      </c>
-      <c s="15" t="str" r="G21"/>
-      <c s="15" t="str" r="H21"/>
-      <c s="16" t="str" r="I21"/>
-      <c s="14" t="inlineStr" r="J21">
-        <is>
-          <t xml:space="preserve">Zugriff</t>
-        </is>
-      </c>
-      <c s="14" t="inlineStr" r="K21">
-        <is>
-          <t xml:space="preserve">Berechtigung</t>
-        </is>
-      </c>
-      <c s="14" t="inlineStr" r="L21">
-        <is>
-          <t xml:space="preserve">Objekttyp</t>
-        </is>
-      </c>
-      <c s="15" t="str" r="M21"/>
-      <c s="16" t="str" r="N21"/>
-      <c s="14" t="inlineStr" r="O21">
-        <is>
-          <t xml:space="preserve">Schema</t>
-        </is>
-      </c>
-      <c s="16" t="str" r="P21"/>
-      <c s="14" t="inlineStr" r="Q21">
-        <is>
-          <t xml:space="preserve">Objektname</t>
-        </is>
-      </c>
-      <c s="14" t="inlineStr" r="R21">
-        <is>
-          <t xml:space="preserve">Spalte</t>
-        </is>
-      </c>
-      <c s="15" t="str" r="S21"/>
-      <c s="15" t="str" r="T21"/>
-      <c s="16" t="str" r="U21"/>
-    </row>
-    <row r="22" ht="17" customHeight="0">
-      <c s="30" t="inlineStr" r="B22">
+      <c s="30" t="inlineStr" r="B21">
         <is>
           <r>
             <rPr>
@@ -13121,55 +13118,55 @@
           </r>
         </is>
       </c>
-      <c s="12" t="str" r="C22"/>
-      <c s="13" t="str" r="D22"/>
-      <c s="30" t="str" r="E22"/>
-      <c s="30" t="inlineStr" r="F22">
+      <c s="12" t="str" r="C21"/>
+      <c s="13" t="str" r="D21"/>
+      <c s="30" t="str" r="E21"/>
+      <c s="30" t="inlineStr" r="F21">
         <is>
           <t xml:space="preserve">DATABASE_ROLE</t>
         </is>
       </c>
-      <c s="12" t="str" r="G22"/>
-      <c s="12" t="str" r="H22"/>
-      <c s="13" t="str" r="I22"/>
-      <c s="30" t="inlineStr" r="J22">
-        <is>
-          <t xml:space="preserve">GRANT</t>
-        </is>
-      </c>
-      <c s="30" t="inlineStr" r="K22">
+      <c s="12" t="str" r="G21"/>
+      <c s="12" t="str" r="H21"/>
+      <c s="13" t="str" r="I21"/>
+      <c s="30" t="inlineStr" r="J21">
+        <is>
+          <t xml:space="preserve">GRANT</t>
+        </is>
+      </c>
+      <c s="30" t="inlineStr" r="K21">
         <is>
           <t xml:space="preserve">VIEW ANY COLUMN ENCRYPTION KEY DEFINITION</t>
         </is>
       </c>
-      <c s="30" t="inlineStr" r="L22">
+      <c s="30" t="inlineStr" r="L21">
         <is>
           <t xml:space="preserve">DATABASE</t>
         </is>
       </c>
-      <c s="12" t="str" r="M22"/>
-      <c s="13" t="str" r="N22"/>
-      <c s="31" t="inlineStr" r="O22">
-        <is>
-          <t xml:space="preserve">*</t>
-        </is>
-      </c>
-      <c s="13" t="str" r="P22"/>
-      <c s="31" t="inlineStr" r="Q22">
-        <is>
-          <t xml:space="preserve">*</t>
-        </is>
-      </c>
-      <c s="31" t="inlineStr" r="R22">
-        <is>
-          <t xml:space="preserve">*</t>
-        </is>
-      </c>
-      <c s="12" t="str" r="S22"/>
-      <c s="12" t="str" r="T22"/>
-      <c s="13" t="str" r="U22"/>
-    </row>
-    <row r="23" ht="0.05" customHeight="1"/>
+      <c s="12" t="str" r="M21"/>
+      <c s="13" t="str" r="N21"/>
+      <c s="31" t="inlineStr" r="O21">
+        <is>
+          <t xml:space="preserve">*</t>
+        </is>
+      </c>
+      <c s="13" t="str" r="P21"/>
+      <c s="31" t="inlineStr" r="Q21">
+        <is>
+          <t xml:space="preserve">*</t>
+        </is>
+      </c>
+      <c s="31" t="inlineStr" r="R21">
+        <is>
+          <t xml:space="preserve">*</t>
+        </is>
+      </c>
+      <c s="12" t="str" r="S21"/>
+      <c s="12" t="str" r="T21"/>
+      <c s="13" t="str" r="U21"/>
+    </row>
+    <row r="22" ht="0.05" customHeight="1"/>
   </sheetData>
   <mergeCells>
     <mergeCell ref="T1:T6"/>
@@ -13192,24 +13189,24 @@
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="H14:L14"/>
     <mergeCell ref="C16:V16"/>
-    <mergeCell ref="B19:U19"/>
+    <mergeCell ref="B18:U18"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="F20:I20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:P20"/>
+    <mergeCell ref="R20:U20"/>
     <mergeCell ref="B21:D21"/>
     <mergeCell ref="F21:I21"/>
     <mergeCell ref="L21:N21"/>
     <mergeCell ref="O21:P21"/>
     <mergeCell ref="R21:U21"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="F22:I22"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="O22:P22"/>
-    <mergeCell ref="R22:U22"/>
   </mergeCells>
   <pageMargins left="0" right="0" top="0" bottom="0.766566929133858" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
     <oddFooter>&amp;L&amp;"Arial,Regular"&amp;7 Bericht '/SQLSERVER_RechteAudit_V6' 
 &amp;"-,Regular"Berichtsverantwortlicher: Markus Hofmann (IB15MH) &amp;C&amp;"Arial,Regular"&amp;10  &amp;R&amp;"Arial,Regular"&amp;7 Generiert von LAN\\ps733 
-&amp;"-,Regular"19.06.2026 10:59:29 Uhr 
+&amp;"-,Regular"19.06.2026 11:01:25 Uhr 
 &amp;"-,Regular"Seite &amp;P von &amp;N </oddFooter>
   </headerFooter>
   <drawing r:id="rId18"/>
